--- a/week-04/Opportunity counties.xlsx
+++ b/week-04/Opportunity counties.xlsx
@@ -8,14 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\onurkaraer\Documents\DataAnalytics\week-04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B27284D-A90A-4065-B693-0E222A03C40D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80E825EE-A02A-4C86-8DA1-B7CA061D39F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DFFEABD4-FC9C-452B-A70A-6717FFEF8536}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{DFFEABD4-FC9C-452B-A70A-6717FFEF8536}"/>
   </bookViews>
   <sheets>
-    <sheet name="data-1777486098589" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="data-1777486098589" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="43" r:id="rId4"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="113">
   <si>
     <t>county</t>
   </si>
@@ -354,6 +359,24 @@
   </si>
   <si>
     <t>AVG Revenue pc</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of bacardi_revenue</t>
+  </si>
+  <si>
+    <t>Sum of bacardi_revenue_per_capita</t>
+  </si>
+  <si>
+    <t>Benchmark</t>
+  </si>
+  <si>
+    <t>Potential Increase in Revenue if it hits the benchmark</t>
   </si>
 </sst>
 </file>
@@ -363,7 +386,7 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -498,8 +521,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="6" tint="-0.249977111117893"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -697,8 +727,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -842,6 +878,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -887,7 +949,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -895,13 +957,35 @@
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="8" fontId="0" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="0" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="0" fillId="35" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="35" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="35" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="35" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="36" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="8" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="8" fontId="18" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="8" fontId="0" fillId="36" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="36" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="36" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="13" fillId="33" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="34" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="36" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -947,54 +1031,31 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="20">
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <color rgb="FFFF0000"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <color theme="6" tint="-0.249977111117893"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -1225,13 +1286,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color theme="4" tint="0.39997558519241921"/>
         </left>
@@ -1245,6 +1299,61 @@
           <color theme="4" tint="0.39997558519241921"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <numFmt numFmtId="12" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
@@ -1271,6 +1380,3954 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Revenue Per Capita Top Performers</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$F$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sum of bacardi_revenue_per_capita</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$E$4:$E$8</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Polk</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Scott</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Linn</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Johnson</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Black Hawk</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$F$4:$F$8</c:f>
+              <c:numCache>
+                <c:formatCode>"$"#,##0.00_);[Red]\("$"#,##0.00\)</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>11.608120471855843</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10.542502723575268</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.0104553416719533</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11.244280649745573</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8.9226179723853836</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A9A4-4EBC-A3F9-780CB49F71E2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1026221535"/>
+        <c:axId val="1026222015"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$G$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Benchmark</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$E$4:$E$8</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Polk</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Scott</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Linn</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Johnson</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Black Hawk</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$G$4:$G$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>11.131634615058895</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>11.131634615058895</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>11.131634615058895</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11.131634615058895</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>11.131634615058895</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-A9A4-4EBC-A3F9-780CB49F71E2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1026221535"/>
+        <c:axId val="1026222015"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1026221535"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1026222015"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1026222015"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1026221535"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'data-1777486098589'!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>bacardi_revenue_per_capita</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'data-1777486098589'!$B$2:$B$100</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="99"/>
+                <c:pt idx="0">
+                  <c:v>430640</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>165224</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>211226</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>130882</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>131090</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>93653</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>93158</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>102172</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>89542</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>66135</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>44151</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>16667</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>40325</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>49116</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>42745</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>35862</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>20816</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>38013</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>40648</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>35625</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>33309</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>33704</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>20260</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>17534</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>24276</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46225</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>21056</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>15543</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>26306</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>21704</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>16355</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>36842</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>24986</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>16667</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>20638</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>17096</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>18914</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>12167</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>19848</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>10866</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>20958</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>16303</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>22381</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>20880</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>20145</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>17764</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>15932</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>13956</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>12534</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>14330</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>14398</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>13229</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>18129</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>16843</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>12884</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>9566</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>9421</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>15673</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>11581</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>10680</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>10350</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>10302</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>26076</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>9815</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>9243</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>17767</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>15059</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>10776</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>12072</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>7598</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>14928</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>9670</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>18499</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>15679</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>9286</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>10740</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>7089</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>9336</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>7682</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>11341</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>6119</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>12439</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>8898</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>14867</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>12453</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>7970</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>6462</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>7310</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>8457</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>11387</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>10954</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>6403</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>7570</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>10511</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>8753</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>5131</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>6317</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>4029</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>7441</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'data-1777486098589'!$F$2:$F$100</c:f>
+              <c:numCache>
+                <c:formatCode>"$"#,##0.00_);[Red]\("$"#,##0.00\)</c:formatCode>
+                <c:ptCount val="99"/>
+                <c:pt idx="0">
+                  <c:v>11.608120471855843</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10.542502723575268</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.0104553416719533</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11.244280649745573</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8.9226179723853836</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8.6240644720404038</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8.5387873290538661</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7.2611199741612182</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>7.9575786781622035</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9.4313566190368192</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9.6241652510701918</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>21.338146037079259</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>7.0433160570365771</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5.733883663164753</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>6.4019742659960235</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>6.804178796497685</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>11.421915353574173</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>6.03421040170468</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>4.2258873745325722</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4.2316494035087722</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>4.1824539914137313</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>3.8475943508188939</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>6.2419141164856855</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>7.0742785445420324</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>4.9977409787444387</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2.4452573282855599</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>5.2656283244680857</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>7.01411825258959</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>3.9437379305101499</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>4.6690683744931816</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>6.1811354325894223</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2.7024719070625918</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>3.9390602737533018</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>5.5107499850002997</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>4.0548342862680489</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>4.4926462330369681</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>3.9358543935708998</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>5.6193005671077501</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>3.3730547158403867</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>5.985504325418737</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>3.0172354232274072</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>3.84859228362878</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>2.7916786560028592</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>2.9565727969348656</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>3.002470588235294</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>3.3766995046160777</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>3.6226217675119257</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>4.1175781026081975</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>4.1798946864528483</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>3.5934682484298675</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>3.4423149048478954</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>3.5416992969990173</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>2.557197859782669</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>2.739189574303865</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>3.5636999379074821</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>4.6949100982646881</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>4.7661723808512901</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>2.5560090601671668</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>3.410603574820827</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>3.5420636704119848</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>3.5899207729468601</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>3.5856154144826249</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.3598055683387023</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>3.5945736118186447</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>3.7766212268743913</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>1.9400512185512466</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>2.147093432498838</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>2.9433769487750556</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>2.3555815109343938</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>3.6572124243221902</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>1.8498271704180065</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>2.8191809720785934</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>1.4671609276177089</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>1.6707761974615727</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>2.8135677363773421</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>2.3902160148975788</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>3.4157836084073918</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>2.43330441302485</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>2.8007732361364228</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>1.739190547570761</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>2.9787154763850299</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>1.2944456949915588</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>1.7552528658125421</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.86707674715813543</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.97823737252067777</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>1.4297038895859473</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>1.7115567935623646</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>1.4146976744186046</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>1.1117240156083719</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.81299376481953101</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.7920339601971883</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>1.1289114477588631</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.80194980184940556</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.53651222528779374</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.63141094481891924</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.88365036055349844</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.41804495804970715</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.64746587242491926</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>4.3542534605563767E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5A46-400A-8461-825373AAB81D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1026247935"/>
+        <c:axId val="1026250335"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1026247935"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1026250335"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1026250335"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1026247935"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>109537</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>185737</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8056436A-D368-13BF-D4CF-4E100689A8DD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>585787</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>52387</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>909637</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>128587</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68474047-536C-D743-4234-58EB7F0D2F9C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="onur karaer" refreshedDate="46142.609170601849" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="99" xr:uid="{E3243782-140E-4964-AC00-C7D182965575}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="Table1"/>
+  </cacheSource>
+  <cacheFields count="6">
+    <cacheField name="county" numFmtId="0">
+      <sharedItems count="99">
+        <s v="Polk"/>
+        <s v="Scott"/>
+        <s v="Linn"/>
+        <s v="Johnson"/>
+        <s v="Black Hawk"/>
+        <s v="Dubuque"/>
+        <s v="Pottawattamie"/>
+        <s v="Woodbury"/>
+        <s v="Story"/>
+        <s v="Dallas"/>
+        <s v="Cerro Gordo"/>
+        <s v="Dickinson"/>
+        <s v="Des Moines"/>
+        <s v="Clinton"/>
+        <s v="Muscatine"/>
+        <s v="Lee"/>
+        <s v="Carroll"/>
+        <s v="Webster"/>
+        <s v="Marshall"/>
+        <s v="Wapello"/>
+        <s v="Marion"/>
+        <s v="Sioux"/>
+        <s v="Buena Vista"/>
+        <s v="Hardin"/>
+        <s v="Bremer"/>
+        <s v="Warren"/>
+        <s v="Winneshiek"/>
+        <s v="Kossuth"/>
+        <s v="Boone"/>
+        <s v="Washington"/>
+        <s v="Iowa"/>
+        <s v="Jasper"/>
+        <s v="Plymouth"/>
+        <s v="Clay"/>
+        <s v="Jones"/>
+        <s v="Crawford"/>
+        <s v="Poweshiek"/>
+        <s v="Shelby"/>
+        <s v="Jackson"/>
+        <s v="Winnebago"/>
+        <s v="Buchanan"/>
+        <s v="Floyd"/>
+        <s v="Mahaska"/>
+        <s v="Fayette"/>
+        <s v="Henry"/>
+        <s v="Delaware"/>
+        <s v="Page"/>
+        <s v="Cass"/>
+        <s v="Union"/>
+        <s v="Allamakee"/>
+        <s v="O'Brien"/>
+        <s v="Wright"/>
+        <s v="Clayton"/>
+        <s v="Jefferson"/>
+        <s v="Appanoose"/>
+        <s v="Howard"/>
+        <s v="Palo Alto"/>
+        <s v="Hamilton"/>
+        <s v="Lyon"/>
+        <s v="Franklin"/>
+        <s v="Sac"/>
+        <s v="Emmet"/>
+        <s v="Benton"/>
+        <s v="Humboldt"/>
+        <s v="Monona"/>
+        <s v="Tama"/>
+        <s v="Mills"/>
+        <s v="Mitchell"/>
+        <s v="Cherokee"/>
+        <s v="Worth"/>
+        <s v="Harrison"/>
+        <s v="Calhoun"/>
+        <s v="Cedar"/>
+        <s v="Madison"/>
+        <s v="Clarke"/>
+        <s v="Montgomery"/>
+        <s v="Ida"/>
+        <s v="Greene"/>
+        <s v="Adair"/>
+        <s v="Hancock"/>
+        <s v="Audubon"/>
+        <s v="Chickasaw"/>
+        <s v="Lucas"/>
+        <s v="Butler"/>
+        <s v="Grundy"/>
+        <s v="Monroe"/>
+        <s v="Osceola"/>
+        <s v="Pocahontas"/>
+        <s v="Decatur"/>
+        <s v="Louisa"/>
+        <s v="Guthrie"/>
+        <s v="Wayne"/>
+        <s v="Van Buren"/>
+        <s v="Keokuk"/>
+        <s v="Davis"/>
+        <s v="Ringgold"/>
+        <s v="Taylor"/>
+        <s v="Adams"/>
+        <s v="Fremont"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="population" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="4029" maxValue="430640"/>
+    </cacheField>
+    <cacheField name="bacardi_revenue" numFmtId="8">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="324" maxValue="4998921"/>
+    </cacheField>
+    <cacheField name="total_market_revenue" numFmtId="8">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="16603.669999999998" maxValue="86397461.790000007"/>
+    </cacheField>
+    <cacheField name="bacardi_market_share_pct" numFmtId="2">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="1.7595422614228091" maxValue="8.1735578645098705"/>
+    </cacheField>
+    <cacheField name="bacardi_revenue_per_capita" numFmtId="8">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="4.3542534605563767E-2" maxValue="21.338146037079259"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="99">
+  <r>
+    <x v="0"/>
+    <n v="430640"/>
+    <n v="4998921"/>
+    <n v="86397461.790000007"/>
+    <n v="5.7859581710288106"/>
+    <n v="11.608120471855843"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="165224"/>
+    <n v="1741874.47"/>
+    <n v="27902848.670000002"/>
+    <n v="6.2426402787783886"/>
+    <n v="10.542502723575268"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="211226"/>
+    <n v="1692016.44"/>
+    <n v="34460047.490000002"/>
+    <n v="4.9100815676211944"/>
+    <n v="8.0104553416719533"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="130882"/>
+    <n v="1471673.94"/>
+    <n v="24200402.25"/>
+    <n v="6.0811961916872681"/>
+    <n v="11.244280649745573"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="131090"/>
+    <n v="1169665.99"/>
+    <n v="22967283.289999999"/>
+    <n v="5.092748564255638"/>
+    <n v="8.9226179723853836"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="93653"/>
+    <n v="807669.51"/>
+    <n v="11879190.380000001"/>
+    <n v="6.7990282516206282"/>
+    <n v="8.6240644720404038"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="93158"/>
+    <n v="795456.35"/>
+    <n v="14177698.300000001"/>
+    <n v="5.6106169927455705"/>
+    <n v="8.5387873290538661"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <n v="102172"/>
+    <n v="741883.15"/>
+    <n v="13242016.16"/>
+    <n v="5.602493918116469"/>
+    <n v="7.2611199741612182"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <n v="89542"/>
+    <n v="712537.51"/>
+    <n v="12267027.18"/>
+    <n v="5.8085589894323526"/>
+    <n v="7.9575786781622035"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <n v="66135"/>
+    <n v="623742.77"/>
+    <n v="7898228.4199999999"/>
+    <n v="7.8972490643667665"/>
+    <n v="9.4313566190368192"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <n v="44151"/>
+    <n v="424916.52"/>
+    <n v="7998958.9199999999"/>
+    <n v="5.3121477963534787"/>
+    <n v="9.6241652510701918"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <n v="16667"/>
+    <n v="355642.88"/>
+    <n v="5142111.9000000004"/>
+    <n v="6.9162804488949376"/>
+    <n v="21.338146037079259"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <n v="40325"/>
+    <n v="284021.71999999997"/>
+    <n v="5168751.09"/>
+    <n v="5.4949777045657653"/>
+    <n v="7.0433160570365771"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <n v="49116"/>
+    <n v="281625.43"/>
+    <n v="4851700.7300000004"/>
+    <n v="5.8046743950754767"/>
+    <n v="5.733883663164753"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <n v="42745"/>
+    <n v="273652.39"/>
+    <n v="4387996.29"/>
+    <n v="6.2363860840912428"/>
+    <n v="6.4019742659960235"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <n v="35862"/>
+    <n v="244011.46"/>
+    <n v="4881120.76"/>
+    <n v="4.9990867261395104"/>
+    <n v="6.804178796497685"/>
+  </r>
+  <r>
+    <x v="16"/>
+    <n v="20816"/>
+    <n v="237758.59"/>
+    <n v="3183557.2"/>
+    <n v="7.4683310229198954"/>
+    <n v="11.421915353574173"/>
+  </r>
+  <r>
+    <x v="17"/>
+    <n v="38013"/>
+    <n v="229378.44"/>
+    <n v="4323049.3"/>
+    <n v="5.3059408783517688"/>
+    <n v="6.03421040170468"/>
+  </r>
+  <r>
+    <x v="18"/>
+    <n v="40648"/>
+    <n v="171773.87"/>
+    <n v="4092699.9"/>
+    <n v="4.1970795366647824"/>
+    <n v="4.2258873745325722"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <n v="35625"/>
+    <n v="150752.51"/>
+    <n v="3658972.86"/>
+    <n v="4.1200772940414767"/>
+    <n v="4.2316494035087722"/>
+  </r>
+  <r>
+    <x v="20"/>
+    <n v="33309"/>
+    <n v="139313.35999999999"/>
+    <n v="2779364.89"/>
+    <n v="5.0124170633816991"/>
+    <n v="4.1824539914137313"/>
+  </r>
+  <r>
+    <x v="21"/>
+    <n v="33704"/>
+    <n v="129679.32"/>
+    <n v="2076294.71"/>
+    <n v="6.2457087317821083"/>
+    <n v="3.8475943508188939"/>
+  </r>
+  <r>
+    <x v="22"/>
+    <n v="20260"/>
+    <n v="126461.18"/>
+    <n v="2432925.21"/>
+    <n v="5.1979065973836489"/>
+    <n v="6.2419141164856855"/>
+  </r>
+  <r>
+    <x v="23"/>
+    <n v="17534"/>
+    <n v="124040.4"/>
+    <n v="2567270.44"/>
+    <n v="4.8316062876492278"/>
+    <n v="7.0742785445420324"/>
+  </r>
+  <r>
+    <x v="24"/>
+    <n v="24276"/>
+    <n v="121325.16"/>
+    <n v="2507674.79"/>
+    <n v="4.8381536746238138"/>
+    <n v="4.9977409787444387"/>
+  </r>
+  <r>
+    <x v="25"/>
+    <n v="46225"/>
+    <n v="113032.02"/>
+    <n v="3028648.21"/>
+    <n v="3.732094722219323"/>
+    <n v="2.4452573282855599"/>
+  </r>
+  <r>
+    <x v="26"/>
+    <n v="21056"/>
+    <n v="110873.07"/>
+    <n v="1956732.65"/>
+    <n v="5.6662349861643087"/>
+    <n v="5.2656283244680857"/>
+  </r>
+  <r>
+    <x v="27"/>
+    <n v="15543"/>
+    <n v="109020.44"/>
+    <n v="2522531.13"/>
+    <n v="4.3218669812808219"/>
+    <n v="7.01411825258959"/>
+  </r>
+  <r>
+    <x v="28"/>
+    <n v="26306"/>
+    <n v="103743.97"/>
+    <n v="2441399.88"/>
+    <n v="4.2493640984368364"/>
+    <n v="3.9437379305101499"/>
+  </r>
+  <r>
+    <x v="29"/>
+    <n v="21704"/>
+    <n v="101337.46"/>
+    <n v="2047974.45"/>
+    <n v="4.948179895506021"/>
+    <n v="4.6690683744931816"/>
+  </r>
+  <r>
+    <x v="30"/>
+    <n v="16355"/>
+    <n v="101092.47"/>
+    <n v="2226471.23"/>
+    <n v="4.5404795102607274"/>
+    <n v="6.1811354325894223"/>
+  </r>
+  <r>
+    <x v="31"/>
+    <n v="36842"/>
+    <n v="99564.47"/>
+    <n v="2544580.83"/>
+    <n v="3.9128043733631364"/>
+    <n v="2.7024719070625918"/>
+  </r>
+  <r>
+    <x v="32"/>
+    <n v="24986"/>
+    <n v="98421.36"/>
+    <n v="2268583.98"/>
+    <n v="4.3384490443241166"/>
+    <n v="3.9390602737533018"/>
+  </r>
+  <r>
+    <x v="33"/>
+    <n v="16667"/>
+    <n v="91847.67"/>
+    <n v="2140888"/>
+    <n v="4.2901669774411362"/>
+    <n v="5.5107499850002997"/>
+  </r>
+  <r>
+    <x v="34"/>
+    <n v="20638"/>
+    <n v="83683.67"/>
+    <n v="1598830.32"/>
+    <n v="5.2340557314424707"/>
+    <n v="4.0548342862680489"/>
+  </r>
+  <r>
+    <x v="35"/>
+    <n v="17096"/>
+    <n v="76806.28"/>
+    <n v="1971876.55"/>
+    <n v="3.8950856228803974"/>
+    <n v="4.4926462330369681"/>
+  </r>
+  <r>
+    <x v="36"/>
+    <n v="18914"/>
+    <n v="74442.75"/>
+    <n v="2012519.27"/>
+    <n v="3.6989832152017108"/>
+    <n v="3.9358543935708998"/>
+  </r>
+  <r>
+    <x v="37"/>
+    <n v="12167"/>
+    <n v="68370.03"/>
+    <n v="1163855.3500000001"/>
+    <n v="5.8744439332602623"/>
+    <n v="5.6193005671077501"/>
+  </r>
+  <r>
+    <x v="38"/>
+    <n v="19848"/>
+    <n v="66948.39"/>
+    <n v="1720246.48"/>
+    <n v="3.8917905531770076"/>
+    <n v="3.3730547158403867"/>
+  </r>
+  <r>
+    <x v="39"/>
+    <n v="10866"/>
+    <n v="65038.49"/>
+    <n v="1024059.83"/>
+    <n v="6.3510439619528878"/>
+    <n v="5.985504325418737"/>
+  </r>
+  <r>
+    <x v="40"/>
+    <n v="20958"/>
+    <n v="63235.22"/>
+    <n v="1949162.4"/>
+    <n v="3.2442253144222359"/>
+    <n v="3.0172354232274072"/>
+  </r>
+  <r>
+    <x v="41"/>
+    <n v="16303"/>
+    <n v="62743.6"/>
+    <n v="1571213.86"/>
+    <n v="3.9933201709409563"/>
+    <n v="3.84859228362878"/>
+  </r>
+  <r>
+    <x v="42"/>
+    <n v="22381"/>
+    <n v="62480.56"/>
+    <n v="1378251.77"/>
+    <n v="4.5333197721922751"/>
+    <n v="2.7916786560028592"/>
+  </r>
+  <r>
+    <x v="43"/>
+    <n v="20880"/>
+    <n v="61733.24"/>
+    <n v="1668008.23"/>
+    <n v="3.7010153121366796"/>
+    <n v="2.9565727969348656"/>
+  </r>
+  <r>
+    <x v="44"/>
+    <n v="20145"/>
+    <n v="60484.77"/>
+    <n v="1550328.8"/>
+    <n v="3.9014156222860592"/>
+    <n v="3.002470588235294"/>
+  </r>
+  <r>
+    <x v="45"/>
+    <n v="17764"/>
+    <n v="59983.69"/>
+    <n v="1277554.19"/>
+    <n v="4.6951973129218105"/>
+    <n v="3.3766995046160777"/>
+  </r>
+  <r>
+    <x v="46"/>
+    <n v="15932"/>
+    <n v="57715.61"/>
+    <n v="1618152.03"/>
+    <n v="3.5667606584530871"/>
+    <n v="3.6226217675119257"/>
+  </r>
+  <r>
+    <x v="47"/>
+    <n v="13956"/>
+    <n v="57464.92"/>
+    <n v="1527535.95"/>
+    <n v="3.7619356847215282"/>
+    <n v="4.1175781026081975"/>
+  </r>
+  <r>
+    <x v="48"/>
+    <n v="12534"/>
+    <n v="52390.8"/>
+    <n v="1337091.6299999999"/>
+    <n v="3.9182654968829631"/>
+    <n v="4.1798946864528483"/>
+  </r>
+  <r>
+    <x v="49"/>
+    <n v="14330"/>
+    <n v="51494.400000000001"/>
+    <n v="1107480.6599999999"/>
+    <n v="4.6496884198411204"/>
+    <n v="3.5934682484298675"/>
+  </r>
+  <r>
+    <x v="50"/>
+    <n v="14398"/>
+    <n v="49562.45"/>
+    <n v="1776809.53"/>
+    <n v="2.7894070334032932"/>
+    <n v="3.4423149048478954"/>
+  </r>
+  <r>
+    <x v="51"/>
+    <n v="13229"/>
+    <n v="46853.14"/>
+    <n v="991451.14"/>
+    <n v="4.7257134627935367"/>
+    <n v="3.5416992969990173"/>
+  </r>
+  <r>
+    <x v="52"/>
+    <n v="18129"/>
+    <n v="46359.44"/>
+    <n v="994568.53"/>
+    <n v="4.6612615020103245"/>
+    <n v="2.557197859782669"/>
+  </r>
+  <r>
+    <x v="53"/>
+    <n v="16843"/>
+    <n v="46136.17"/>
+    <n v="1120768.6100000001"/>
+    <n v="4.1164759244997056"/>
+    <n v="2.739189574303865"/>
+  </r>
+  <r>
+    <x v="54"/>
+    <n v="12884"/>
+    <n v="45914.71"/>
+    <n v="1089064.58"/>
+    <n v="4.2159767972621056"/>
+    <n v="3.5636999379074821"/>
+  </r>
+  <r>
+    <x v="55"/>
+    <n v="9566"/>
+    <n v="44911.51"/>
+    <n v="1114317.54"/>
+    <n v="4.0304050136373153"/>
+    <n v="4.6949100982646881"/>
+  </r>
+  <r>
+    <x v="56"/>
+    <n v="9421"/>
+    <n v="44902.11"/>
+    <n v="941404.65"/>
+    <n v="4.7696928201916151"/>
+    <n v="4.7661723808512901"/>
+  </r>
+  <r>
+    <x v="57"/>
+    <n v="15673"/>
+    <n v="40060.33"/>
+    <n v="1244371.58"/>
+    <n v="3.2193221577754132"/>
+    <n v="2.5560090601671668"/>
+  </r>
+  <r>
+    <x v="58"/>
+    <n v="11581"/>
+    <n v="39498.199999999997"/>
+    <n v="1024856.07"/>
+    <n v="3.8540241070143635"/>
+    <n v="3.410603574820827"/>
+  </r>
+  <r>
+    <x v="59"/>
+    <n v="10680"/>
+    <n v="37829.24"/>
+    <n v="702357.9"/>
+    <n v="5.3860346697887209"/>
+    <n v="3.5420636704119848"/>
+  </r>
+  <r>
+    <x v="60"/>
+    <n v="10350"/>
+    <n v="37155.68"/>
+    <n v="746083.11"/>
+    <n v="4.9800993350459306"/>
+    <n v="3.5899207729468601"/>
+  </r>
+  <r>
+    <x v="61"/>
+    <n v="10302"/>
+    <n v="36939.01"/>
+    <n v="840077.29"/>
+    <n v="4.3970966052421199"/>
+    <n v="3.5856154144826249"/>
+  </r>
+  <r>
+    <x v="62"/>
+    <n v="26076"/>
+    <n v="35458.29"/>
+    <n v="994344.98"/>
+    <n v="3.5659947717541653"/>
+    <n v="1.3598055683387023"/>
+  </r>
+  <r>
+    <x v="63"/>
+    <n v="9815"/>
+    <n v="35280.74"/>
+    <n v="940960.97"/>
+    <n v="3.74943713127655"/>
+    <n v="3.5945736118186447"/>
+  </r>
+  <r>
+    <x v="64"/>
+    <n v="9243"/>
+    <n v="34907.31"/>
+    <n v="790327.5"/>
+    <n v="4.416815813697486"/>
+    <n v="3.7766212268743913"/>
+  </r>
+  <r>
+    <x v="65"/>
+    <n v="17767"/>
+    <n v="34468.89"/>
+    <n v="876011.17"/>
+    <n v="3.9347546219073894"/>
+    <n v="1.9400512185512466"/>
+  </r>
+  <r>
+    <x v="66"/>
+    <n v="15059"/>
+    <n v="32333.08"/>
+    <n v="617724.37"/>
+    <n v="5.23422444868089"/>
+    <n v="2.147093432498838"/>
+  </r>
+  <r>
+    <x v="67"/>
+    <n v="10776"/>
+    <n v="31717.83"/>
+    <n v="644715.72"/>
+    <n v="4.9196613353867038"/>
+    <n v="2.9433769487750556"/>
+  </r>
+  <r>
+    <x v="68"/>
+    <n v="12072"/>
+    <n v="28436.58"/>
+    <n v="981007.93"/>
+    <n v="2.898710512972102"/>
+    <n v="2.3555815109343938"/>
+  </r>
+  <r>
+    <x v="69"/>
+    <n v="7598"/>
+    <n v="27787.5"/>
+    <n v="339968.23"/>
+    <n v="8.1735578645098705"/>
+    <n v="3.6572124243221902"/>
+  </r>
+  <r>
+    <x v="70"/>
+    <n v="14928"/>
+    <n v="27614.22"/>
+    <n v="651345.05000000005"/>
+    <n v="4.2395685666145768"/>
+    <n v="1.8498271704180065"/>
+  </r>
+  <r>
+    <x v="71"/>
+    <n v="9670"/>
+    <n v="27261.48"/>
+    <n v="482178.34"/>
+    <n v="5.6538168014763999"/>
+    <n v="2.8191809720785934"/>
+  </r>
+  <r>
+    <x v="72"/>
+    <n v="18499"/>
+    <n v="27141.01"/>
+    <n v="783200.87"/>
+    <n v="3.4653957930358277"/>
+    <n v="1.4671609276177089"/>
+  </r>
+  <r>
+    <x v="73"/>
+    <n v="15679"/>
+    <n v="26196.1"/>
+    <n v="848829.42"/>
+    <n v="3.0861442102230621"/>
+    <n v="1.6707761974615727"/>
+  </r>
+  <r>
+    <x v="74"/>
+    <n v="9286"/>
+    <n v="26126.79"/>
+    <n v="845731.43"/>
+    <n v="3.0892537599081544"/>
+    <n v="2.8135677363773421"/>
+  </r>
+  <r>
+    <x v="75"/>
+    <n v="10740"/>
+    <n v="25670.92"/>
+    <n v="839109.2"/>
+    <n v="3.0593062261741379"/>
+    <n v="2.3902160148975788"/>
+  </r>
+  <r>
+    <x v="76"/>
+    <n v="7089"/>
+    <n v="24214.49"/>
+    <n v="603641"/>
+    <n v="4.0114057858892949"/>
+    <n v="3.4157836084073918"/>
+  </r>
+  <r>
+    <x v="77"/>
+    <n v="9336"/>
+    <n v="22717.33"/>
+    <n v="548905.25"/>
+    <n v="4.1386614538665834"/>
+    <n v="2.43330441302485"/>
+  </r>
+  <r>
+    <x v="78"/>
+    <n v="7682"/>
+    <n v="21515.54"/>
+    <n v="603088.67000000004"/>
+    <n v="3.5675583160930544"/>
+    <n v="2.8007732361364228"/>
+  </r>
+  <r>
+    <x v="79"/>
+    <n v="11341"/>
+    <n v="19724.16"/>
+    <n v="399807.53"/>
+    <n v="4.9334138354022494"/>
+    <n v="1.739190547570761"/>
+  </r>
+  <r>
+    <x v="80"/>
+    <n v="6119"/>
+    <n v="18226.759999999998"/>
+    <n v="241821.88"/>
+    <n v="7.5372666857109856"/>
+    <n v="2.9787154763850299"/>
+  </r>
+  <r>
+    <x v="81"/>
+    <n v="12439"/>
+    <n v="16101.61"/>
+    <n v="548956.25"/>
+    <n v="2.9331317386403746"/>
+    <n v="1.2944456949915588"/>
+  </r>
+  <r>
+    <x v="82"/>
+    <n v="8898"/>
+    <n v="15618.24"/>
+    <n v="580658.38"/>
+    <n v="2.6897467664205585"/>
+    <n v="1.7552528658125421"/>
+  </r>
+  <r>
+    <x v="83"/>
+    <n v="14867"/>
+    <n v="12890.83"/>
+    <n v="399080.61"/>
+    <n v="3.2301318773668304"/>
+    <n v="0.86707674715813543"/>
+  </r>
+  <r>
+    <x v="84"/>
+    <n v="12453"/>
+    <n v="12181.99"/>
+    <n v="405592.83"/>
+    <n v="3.0035023055018009"/>
+    <n v="0.97823737252067777"/>
+  </r>
+  <r>
+    <x v="85"/>
+    <n v="7970"/>
+    <n v="11394.74"/>
+    <n v="417543.16"/>
+    <n v="2.7289969257309834"/>
+    <n v="1.4297038895859473"/>
+  </r>
+  <r>
+    <x v="86"/>
+    <n v="6462"/>
+    <n v="11060.08"/>
+    <n v="344176.87"/>
+    <n v="3.2134872979697908"/>
+    <n v="1.7115567935623646"/>
+  </r>
+  <r>
+    <x v="87"/>
+    <n v="7310"/>
+    <n v="10341.44"/>
+    <n v="500771.13"/>
+    <n v="2.065103074132888"/>
+    <n v="1.4146976744186046"/>
+  </r>
+  <r>
+    <x v="88"/>
+    <n v="8457"/>
+    <n v="9401.85"/>
+    <n v="248492.15"/>
+    <n v="3.7835601647778412"/>
+    <n v="1.1117240156083719"/>
+  </r>
+  <r>
+    <x v="89"/>
+    <n v="11387"/>
+    <n v="9257.56"/>
+    <n v="351079.49"/>
+    <n v="2.6368843135781015"/>
+    <n v="0.81299376481953101"/>
+  </r>
+  <r>
+    <x v="90"/>
+    <n v="10954"/>
+    <n v="8675.94"/>
+    <n v="382753.71"/>
+    <n v="2.2667161083820715"/>
+    <n v="0.7920339601971883"/>
+  </r>
+  <r>
+    <x v="91"/>
+    <n v="6403"/>
+    <n v="7228.42"/>
+    <n v="98824.4"/>
+    <n v="7.3144081825945824"/>
+    <n v="1.1289114477588631"/>
+  </r>
+  <r>
+    <x v="92"/>
+    <n v="7570"/>
+    <n v="6070.76"/>
+    <n v="260151.48"/>
+    <n v="2.3335481312656765"/>
+    <n v="0.80194980184940556"/>
+  </r>
+  <r>
+    <x v="93"/>
+    <n v="10511"/>
+    <n v="5639.28"/>
+    <n v="212602.13"/>
+    <n v="2.6525039989016101"/>
+    <n v="0.53651222528779374"/>
+  </r>
+  <r>
+    <x v="94"/>
+    <n v="8753"/>
+    <n v="5526.74"/>
+    <n v="140947.39000000001"/>
+    <n v="3.9211368156586648"/>
+    <n v="0.63141094481891924"/>
+  </r>
+  <r>
+    <x v="95"/>
+    <n v="5131"/>
+    <n v="4534.01"/>
+    <n v="198067.73"/>
+    <n v="2.2891209991652857"/>
+    <n v="0.88365036055349844"/>
+  </r>
+  <r>
+    <x v="96"/>
+    <n v="6317"/>
+    <n v="2640.79"/>
+    <n v="150083.92000000001"/>
+    <n v="1.7595422614228091"/>
+    <n v="0.41804495804970715"/>
+  </r>
+  <r>
+    <x v="97"/>
+    <n v="4029"/>
+    <n v="2608.64"/>
+    <n v="125714.47"/>
+    <n v="2.075051503617682"/>
+    <n v="0.64746587242491926"/>
+  </r>
+  <r>
+    <x v="98"/>
+    <n v="7441"/>
+    <n v="324"/>
+    <n v="16603.669999999998"/>
+    <n v="1.9513758102877259"/>
+    <n v="4.3542534605563767E-2"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{365ECA7E-30F1-49D9-BBC8-AE1182706ACB}" name="PivotTable19" cacheId="43" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:C103" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="6">
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="100">
+        <item x="78"/>
+        <item x="97"/>
+        <item x="49"/>
+        <item x="54"/>
+        <item x="80"/>
+        <item x="62"/>
+        <item x="4"/>
+        <item x="28"/>
+        <item x="24"/>
+        <item x="40"/>
+        <item x="22"/>
+        <item x="83"/>
+        <item x="71"/>
+        <item x="16"/>
+        <item x="47"/>
+        <item x="72"/>
+        <item x="10"/>
+        <item x="68"/>
+        <item x="81"/>
+        <item x="74"/>
+        <item x="33"/>
+        <item x="52"/>
+        <item x="13"/>
+        <item x="35"/>
+        <item x="9"/>
+        <item x="94"/>
+        <item x="88"/>
+        <item x="45"/>
+        <item x="12"/>
+        <item x="11"/>
+        <item x="5"/>
+        <item x="61"/>
+        <item x="43"/>
+        <item x="41"/>
+        <item x="59"/>
+        <item x="98"/>
+        <item x="77"/>
+        <item x="84"/>
+        <item x="90"/>
+        <item x="57"/>
+        <item x="79"/>
+        <item x="23"/>
+        <item x="70"/>
+        <item x="44"/>
+        <item x="55"/>
+        <item x="63"/>
+        <item x="76"/>
+        <item x="30"/>
+        <item x="38"/>
+        <item x="31"/>
+        <item x="53"/>
+        <item x="3"/>
+        <item x="34"/>
+        <item x="93"/>
+        <item x="27"/>
+        <item x="15"/>
+        <item x="2"/>
+        <item x="89"/>
+        <item x="82"/>
+        <item x="58"/>
+        <item x="73"/>
+        <item x="42"/>
+        <item x="20"/>
+        <item x="18"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="64"/>
+        <item x="85"/>
+        <item x="75"/>
+        <item x="14"/>
+        <item x="50"/>
+        <item x="86"/>
+        <item x="46"/>
+        <item x="56"/>
+        <item x="32"/>
+        <item x="87"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="36"/>
+        <item x="95"/>
+        <item x="60"/>
+        <item x="1"/>
+        <item x="37"/>
+        <item x="21"/>
+        <item x="8"/>
+        <item x="65"/>
+        <item x="96"/>
+        <item x="48"/>
+        <item x="92"/>
+        <item x="19"/>
+        <item x="25"/>
+        <item x="29"/>
+        <item x="91"/>
+        <item x="17"/>
+        <item x="39"/>
+        <item x="26"/>
+        <item x="7"/>
+        <item x="69"/>
+        <item x="51"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="8" showAll="0"/>
+    <pivotField numFmtId="8" showAll="0"/>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField dataField="1" numFmtId="8" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="100">
+    <i>
+      <x v="76"/>
+    </i>
+    <i>
+      <x v="81"/>
+    </i>
+    <i>
+      <x v="56"/>
+    </i>
+    <i>
+      <x v="51"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="30"/>
+    </i>
+    <i>
+      <x v="77"/>
+    </i>
+    <i>
+      <x v="96"/>
+    </i>
+    <i>
+      <x v="84"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="29"/>
+    </i>
+    <i>
+      <x v="28"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="69"/>
+    </i>
+    <i>
+      <x v="55"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="93"/>
+    </i>
+    <i>
+      <x v="63"/>
+    </i>
+    <i>
+      <x v="89"/>
+    </i>
+    <i>
+      <x v="62"/>
+    </i>
+    <i>
+      <x v="83"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="41"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="90"/>
+    </i>
+    <i>
+      <x v="95"/>
+    </i>
+    <i>
+      <x v="54"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="91"/>
+    </i>
+    <i>
+      <x v="47"/>
+    </i>
+    <i>
+      <x v="49"/>
+    </i>
+    <i>
+      <x v="74"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="52"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="78"/>
+    </i>
+    <i>
+      <x v="82"/>
+    </i>
+    <i>
+      <x v="48"/>
+    </i>
+    <i>
+      <x v="94"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="33"/>
+    </i>
+    <i>
+      <x v="61"/>
+    </i>
+    <i>
+      <x v="32"/>
+    </i>
+    <i>
+      <x v="43"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="72"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="87"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="70"/>
+    </i>
+    <i>
+      <x v="98"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="50"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="44"/>
+    </i>
+    <i>
+      <x v="73"/>
+    </i>
+    <i>
+      <x v="39"/>
+    </i>
+    <i>
+      <x v="59"/>
+    </i>
+    <i>
+      <x v="34"/>
+    </i>
+    <i>
+      <x v="80"/>
+    </i>
+    <i>
+      <x v="31"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="45"/>
+    </i>
+    <i>
+      <x v="66"/>
+    </i>
+    <i>
+      <x v="85"/>
+    </i>
+    <i>
+      <x v="64"/>
+    </i>
+    <i>
+      <x v="65"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="97"/>
+    </i>
+    <i>
+      <x v="42"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="60"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="68"/>
+    </i>
+    <i>
+      <x v="46"/>
+    </i>
+    <i>
+      <x v="36"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="40"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="58"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="37"/>
+    </i>
+    <i>
+      <x v="67"/>
+    </i>
+    <i>
+      <x v="71"/>
+    </i>
+    <i>
+      <x v="75"/>
+    </i>
+    <i>
+      <x v="26"/>
+    </i>
+    <i>
+      <x v="57"/>
+    </i>
+    <i>
+      <x v="38"/>
+    </i>
+    <i>
+      <x v="92"/>
+    </i>
+    <i>
+      <x v="88"/>
+    </i>
+    <i>
+      <x v="53"/>
+    </i>
+    <i>
+      <x v="25"/>
+    </i>
+    <i>
+      <x v="79"/>
+    </i>
+    <i>
+      <x v="86"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="35"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Sum of bacardi_revenue" fld="2" baseField="0" baseItem="0" numFmtId="8"/>
+    <dataField name="Sum of bacardi_revenue_per_capita" fld="5" baseField="0" baseItem="0" numFmtId="8"/>
+  </dataFields>
+  <formats count="3">
+    <format dxfId="3">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1">
+            <x v="56"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="2">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="1">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1">
+            <x v="29"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{983D8523-C8ED-4727-AE20-072B7FB5F329}" name="Table1" displayName="Table1" ref="A1:F100" totalsRowShown="0">
   <autoFilter ref="A1:F100" xr:uid="{983D8523-C8ED-4727-AE20-072B7FB5F329}"/>
@@ -1280,12 +5337,12 @@
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{3B119417-A798-4DFE-8DF5-070C981E7B10}" name="county"/>
     <tableColumn id="2" xr3:uid="{17D6E388-C940-4B77-AF81-0DD867D274E8}" name="population"/>
-    <tableColumn id="3" xr3:uid="{A4A1E547-4D15-4736-BF19-2D35E8294503}" name="bacardi_revenue" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{28FFB984-004B-4FD2-BB07-41D67E077A42}" name="total_market_revenue" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{098A1DA7-660D-4961-A93B-0F82D448927D}" name="bacardi_market_share_pct" dataDxfId="12">
+    <tableColumn id="3" xr3:uid="{A4A1E547-4D15-4736-BF19-2D35E8294503}" name="bacardi_revenue" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{28FFB984-004B-4FD2-BB07-41D67E077A42}" name="total_market_revenue" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{098A1DA7-660D-4961-A93B-0F82D448927D}" name="bacardi_market_share_pct" dataDxfId="17">
       <calculatedColumnFormula>C2/D2*100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{DD0D5946-CBFC-44F7-974B-C05B843016CA}" name="bacardi_revenue_per_capita" dataDxfId="11">
+    <tableColumn id="6" xr3:uid="{DD0D5946-CBFC-44F7-974B-C05B843016CA}" name="bacardi_revenue_per_capita" dataDxfId="16">
       <calculatedColumnFormula>C2/B2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1294,20 +5351,20 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{061C1EA0-E225-4ABC-B3BB-96F6F7723D17}" name="Table2" displayName="Table2" ref="L1:Q67" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" headerRowBorderDxfId="9" tableBorderDxfId="10" totalsRowBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{061C1EA0-E225-4ABC-B3BB-96F6F7723D17}" name="Table2" displayName="Table2" ref="L1:Q67" totalsRowShown="0" headerRowDxfId="15" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12" totalsRowBorderDxfId="11">
   <autoFilter ref="L1:Q67" xr:uid="{061C1EA0-E225-4ABC-B3BB-96F6F7723D17}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="L2:Q67">
     <sortCondition descending="1" ref="Q1:Q67"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{8E65B2CA-1843-4E1E-91F3-2CB1BAD44C6E}" name="county" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{7200A321-9B92-4D9C-9FDB-BCD24474BD0E}" name="population" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{5365F2DE-E05A-4460-A698-09A50770FD84}" name="bacardi_revenue" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{A2C70378-0CA0-4A16-AB92-BB75A22A61D8}" name="total_market_revenue" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{2B825ED9-0940-4CEF-A492-9DA22E0FE5D3}" name="bacardi_market_share_pct" dataDxfId="3">
+    <tableColumn id="1" xr3:uid="{8E65B2CA-1843-4E1E-91F3-2CB1BAD44C6E}" name="county" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{7200A321-9B92-4D9C-9FDB-BCD24474BD0E}" name="population" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{5365F2DE-E05A-4460-A698-09A50770FD84}" name="bacardi_revenue" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{A2C70378-0CA0-4A16-AB92-BB75A22A61D8}" name="total_market_revenue" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{2B825ED9-0940-4CEF-A492-9DA22E0FE5D3}" name="bacardi_market_share_pct" dataDxfId="6">
       <calculatedColumnFormula>N2/O2*100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{F10AE5A4-5B8E-4984-8D31-88A1C31F17B7}" name="bacardi_revenue_per_capita" dataDxfId="2">
+    <tableColumn id="6" xr3:uid="{F10AE5A4-5B8E-4984-8D31-88A1C31F17B7}" name="bacardi_revenue_per_capita" dataDxfId="5">
       <calculatedColumnFormula>N2/M2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1631,6 +5688,1267 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EC88510-D2D1-4769-ACA8-D0E796072DF5}">
+  <dimension ref="A3:K103"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="B3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="G3" t="s">
+        <v>111</v>
+      </c>
+      <c r="J3" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="K3" s="19" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="1">
+        <v>4998921</v>
+      </c>
+      <c r="C4" s="1">
+        <v>11.608120471855843</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="F4" s="1">
+        <v>11.608120471855843</v>
+      </c>
+      <c r="G4">
+        <v>11.131634615058895</v>
+      </c>
+      <c r="J4" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="K4" s="1">
+        <v>11.608120471855843</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1741874.47</v>
+      </c>
+      <c r="C5" s="1">
+        <v>10.542502723575268</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="F5" s="1">
+        <v>10.542502723575268</v>
+      </c>
+      <c r="G5">
+        <v>11.131634615058895</v>
+      </c>
+      <c r="J5" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="K5" s="1">
+        <v>10.542502723575268</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1692016.44</v>
+      </c>
+      <c r="C6" s="20">
+        <v>8.0104553416719533</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" s="20">
+        <v>8.0104553416719533</v>
+      </c>
+      <c r="G6">
+        <v>11.131634615058895</v>
+      </c>
+      <c r="J6" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="K6" s="1">
+        <v>11.244280649745573</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="B7" s="1">
+        <v>1471673.94</v>
+      </c>
+      <c r="C7" s="1">
+        <v>11.244280649745573</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="F7" s="1">
+        <v>11.244280649745573</v>
+      </c>
+      <c r="G7">
+        <v>11.131634615058895</v>
+      </c>
+      <c r="K7" s="1">
+        <f>AVERAGE(K4:K6)</f>
+        <v>11.131634615058895</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="1">
+        <v>1169665.99</v>
+      </c>
+      <c r="C8" s="20">
+        <v>8.9226179723853836</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="F8" s="20">
+        <v>8.9226179723853836</v>
+      </c>
+      <c r="G8">
+        <v>11.131634615058895</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="B9" s="1">
+        <v>807669.51</v>
+      </c>
+      <c r="C9" s="1">
+        <v>8.6240644720404038</v>
+      </c>
+      <c r="F9" s="1">
+        <f>AVERAGE(F4:F8)</f>
+        <v>10.065595431846804</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" s="1">
+        <v>795456.35</v>
+      </c>
+      <c r="C10" s="1">
+        <v>8.5387873290538661</v>
+      </c>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" s="1">
+        <v>741883.15</v>
+      </c>
+      <c r="C11" s="1">
+        <v>7.2611199741612182</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12" s="1">
+        <v>712537.51</v>
+      </c>
+      <c r="C12" s="1">
+        <v>7.9575786781622035</v>
+      </c>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13" s="1">
+        <v>623742.77</v>
+      </c>
+      <c r="C13" s="1">
+        <v>9.4313566190368192</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" s="20">
+        <v>8.0104553416719533</v>
+      </c>
+      <c r="G13">
+        <v>11.131634615058895</v>
+      </c>
+      <c r="H13" s="16">
+        <v>211226</v>
+      </c>
+      <c r="I13" s="1">
+        <f>(G13-F13)*H13</f>
+        <v>659274.21320043004</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="1">
+        <v>424916.52</v>
+      </c>
+      <c r="C14" s="1">
+        <v>9.6241652510701918</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="F14" s="20">
+        <v>8.9226179723853836</v>
+      </c>
+      <c r="G14">
+        <v>11.131634615058895</v>
+      </c>
+      <c r="H14" s="16">
+        <v>131090</v>
+      </c>
+      <c r="I14" s="1">
+        <f>(G14-F14)*H14</f>
+        <v>289579.99168807053</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="B15" s="1">
+        <v>355642.88</v>
+      </c>
+      <c r="C15" s="21">
+        <v>21.338146037079259</v>
+      </c>
+      <c r="I15" s="22">
+        <f>SUM(I13:I14)</f>
+        <v>948854.20488850051</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="1">
+        <v>284021.71999999997</v>
+      </c>
+      <c r="C16" s="1">
+        <v>7.0433160570365771</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" s="1">
+        <v>281625.43</v>
+      </c>
+      <c r="C17" s="1">
+        <v>5.733883663164753</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="B18" s="1">
+        <v>273652.39</v>
+      </c>
+      <c r="C18" s="1">
+        <v>6.4019742659960235</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="1">
+        <v>244011.46</v>
+      </c>
+      <c r="C19" s="1">
+        <v>6.804178796497685</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="B20" s="1">
+        <v>237758.59</v>
+      </c>
+      <c r="C20" s="1">
+        <v>11.421915353574173</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" s="1">
+        <v>229378.44</v>
+      </c>
+      <c r="C21" s="1">
+        <v>6.03421040170468</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="1">
+        <v>171773.87</v>
+      </c>
+      <c r="C22" s="1">
+        <v>4.2258873745325722</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="1">
+        <v>150752.51</v>
+      </c>
+      <c r="C23" s="1">
+        <v>4.2316494035087722</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" s="1">
+        <v>139313.35999999999</v>
+      </c>
+      <c r="C24" s="1">
+        <v>4.1824539914137313</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" s="1">
+        <v>129679.32</v>
+      </c>
+      <c r="C25" s="1">
+        <v>3.8475943508188939</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" s="1">
+        <v>126461.18</v>
+      </c>
+      <c r="C26" s="1">
+        <v>6.2419141164856855</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B27" s="1">
+        <v>124040.4</v>
+      </c>
+      <c r="C27" s="1">
+        <v>7.0742785445420324</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" s="1">
+        <v>121325.16</v>
+      </c>
+      <c r="C28" s="1">
+        <v>4.9977409787444387</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" s="1">
+        <v>113032.02</v>
+      </c>
+      <c r="C29" s="1">
+        <v>2.4452573282855599</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="B30" s="1">
+        <v>110873.07</v>
+      </c>
+      <c r="C30" s="1">
+        <v>5.2656283244680857</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="B31" s="1">
+        <v>109020.44</v>
+      </c>
+      <c r="C31" s="1">
+        <v>7.01411825258959</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="B32" s="1">
+        <v>103743.97</v>
+      </c>
+      <c r="C32" s="1">
+        <v>3.9437379305101499</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="B33" s="1">
+        <v>101337.46</v>
+      </c>
+      <c r="C33" s="1">
+        <v>4.6690683744931816</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="B34" s="1">
+        <v>101092.47</v>
+      </c>
+      <c r="C34" s="1">
+        <v>6.1811354325894223</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="1">
+        <v>99564.47</v>
+      </c>
+      <c r="C35" s="1">
+        <v>2.7024719070625918</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B36" s="1">
+        <v>98421.36</v>
+      </c>
+      <c r="C36" s="1">
+        <v>3.9390602737533018</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="B37" s="1">
+        <v>91847.67</v>
+      </c>
+      <c r="C37" s="1">
+        <v>5.5107499850002997</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="B38" s="1">
+        <v>83683.67</v>
+      </c>
+      <c r="C38" s="1">
+        <v>4.0548342862680489</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="1">
+        <v>76806.28</v>
+      </c>
+      <c r="C39" s="1">
+        <v>4.4926462330369681</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B40" s="1">
+        <v>74442.75</v>
+      </c>
+      <c r="C40" s="1">
+        <v>3.9358543935708998</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B41" s="1">
+        <v>68370.03</v>
+      </c>
+      <c r="C41" s="1">
+        <v>5.6193005671077501</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B42" s="1">
+        <v>66948.39</v>
+      </c>
+      <c r="C42" s="1">
+        <v>3.3730547158403867</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="B43" s="1">
+        <v>65038.49</v>
+      </c>
+      <c r="C43" s="1">
+        <v>5.985504325418737</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B44" s="1">
+        <v>63235.22</v>
+      </c>
+      <c r="C44" s="1">
+        <v>3.0172354232274072</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="B45" s="1">
+        <v>62743.6</v>
+      </c>
+      <c r="C45" s="1">
+        <v>3.84859228362878</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="B46" s="1">
+        <v>62480.56</v>
+      </c>
+      <c r="C46" s="1">
+        <v>2.7916786560028592</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B47" s="1">
+        <v>61733.24</v>
+      </c>
+      <c r="C47" s="1">
+        <v>2.9565727969348656</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B48" s="1">
+        <v>60484.77</v>
+      </c>
+      <c r="C48" s="1">
+        <v>3.002470588235294</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="B49" s="1">
+        <v>59983.69</v>
+      </c>
+      <c r="C49" s="1">
+        <v>3.3766995046160777</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B50" s="1">
+        <v>57715.61</v>
+      </c>
+      <c r="C50" s="1">
+        <v>3.6226217675119257</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B51" s="1">
+        <v>57464.92</v>
+      </c>
+      <c r="C51" s="1">
+        <v>4.1175781026081975</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B52" s="1">
+        <v>52390.8</v>
+      </c>
+      <c r="C52" s="1">
+        <v>4.1798946864528483</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="B53" s="1">
+        <v>51494.400000000001</v>
+      </c>
+      <c r="C53" s="1">
+        <v>3.5934682484298675</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B54" s="1">
+        <v>49562.45</v>
+      </c>
+      <c r="C54" s="1">
+        <v>3.4423149048478954</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="B55" s="1">
+        <v>46853.14</v>
+      </c>
+      <c r="C55" s="1">
+        <v>3.5416992969990173</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="B56" s="1">
+        <v>46359.44</v>
+      </c>
+      <c r="C56" s="1">
+        <v>2.557197859782669</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B57" s="1">
+        <v>46136.17</v>
+      </c>
+      <c r="C57" s="1">
+        <v>2.739189574303865</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="B58" s="1">
+        <v>45914.71</v>
+      </c>
+      <c r="C58" s="1">
+        <v>3.5636999379074821</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B59" s="1">
+        <v>44911.51</v>
+      </c>
+      <c r="C59" s="1">
+        <v>4.6949100982646881</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="B60" s="1">
+        <v>44902.11</v>
+      </c>
+      <c r="C60" s="1">
+        <v>4.7661723808512901</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B61" s="1">
+        <v>40060.33</v>
+      </c>
+      <c r="C61" s="1">
+        <v>2.5560090601671668</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B62" s="1">
+        <v>39498.199999999997</v>
+      </c>
+      <c r="C62" s="1">
+        <v>3.410603574820827</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="B63" s="1">
+        <v>37829.24</v>
+      </c>
+      <c r="C63" s="1">
+        <v>3.5420636704119848</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="B64" s="1">
+        <v>37155.68</v>
+      </c>
+      <c r="C64" s="1">
+        <v>3.5899207729468601</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B65" s="1">
+        <v>36939.01</v>
+      </c>
+      <c r="C65" s="1">
+        <v>3.5856154144826249</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B66" s="1">
+        <v>35458.29</v>
+      </c>
+      <c r="C66" s="1">
+        <v>1.3598055683387023</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B67" s="1">
+        <v>35280.74</v>
+      </c>
+      <c r="C67" s="1">
+        <v>3.5945736118186447</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B68" s="1">
+        <v>34907.31</v>
+      </c>
+      <c r="C68" s="1">
+        <v>3.7766212268743913</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B69" s="1">
+        <v>34468.89</v>
+      </c>
+      <c r="C69" s="1">
+        <v>1.9400512185512466</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="B70" s="1">
+        <v>32333.08</v>
+      </c>
+      <c r="C70" s="1">
+        <v>2.147093432498838</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="B71" s="1">
+        <v>31717.83</v>
+      </c>
+      <c r="C71" s="1">
+        <v>2.9433769487750556</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B72" s="1">
+        <v>28436.58</v>
+      </c>
+      <c r="C72" s="1">
+        <v>2.3555815109343938</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="B73" s="1">
+        <v>27787.5</v>
+      </c>
+      <c r="C73" s="1">
+        <v>3.6572124243221902</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B74" s="1">
+        <v>27614.22</v>
+      </c>
+      <c r="C74" s="1">
+        <v>1.8498271704180065</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B75" s="1">
+        <v>27261.48</v>
+      </c>
+      <c r="C75" s="1">
+        <v>2.8191809720785934</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B76" s="1">
+        <v>27141.01</v>
+      </c>
+      <c r="C76" s="1">
+        <v>1.4671609276177089</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B77" s="1">
+        <v>26196.1</v>
+      </c>
+      <c r="C77" s="1">
+        <v>1.6707761974615727</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B78" s="1">
+        <v>26126.79</v>
+      </c>
+      <c r="C78" s="1">
+        <v>2.8135677363773421</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B79" s="1">
+        <v>25670.92</v>
+      </c>
+      <c r="C79" s="1">
+        <v>2.3902160148975788</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B80" s="1">
+        <v>24214.49</v>
+      </c>
+      <c r="C80" s="1">
+        <v>3.4157836084073918</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="B81" s="1">
+        <v>22717.33</v>
+      </c>
+      <c r="C81" s="1">
+        <v>2.43330441302485</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B82" s="1">
+        <v>21515.54</v>
+      </c>
+      <c r="C82" s="1">
+        <v>2.8007732361364228</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="B83" s="1">
+        <v>19724.16</v>
+      </c>
+      <c r="C83" s="1">
+        <v>1.739190547570761</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="B84" s="1">
+        <v>18226.759999999998</v>
+      </c>
+      <c r="C84" s="1">
+        <v>2.9787154763850299</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B85" s="1">
+        <v>16101.61</v>
+      </c>
+      <c r="C85" s="1">
+        <v>1.2944456949915588</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" s="1">
+        <v>15618.24</v>
+      </c>
+      <c r="C86" s="1">
+        <v>1.7552528658125421</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B87" s="1">
+        <v>12890.83</v>
+      </c>
+      <c r="C87" s="1">
+        <v>0.86707674715813543</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B88" s="1">
+        <v>12181.99</v>
+      </c>
+      <c r="C88" s="1">
+        <v>0.97823737252067777</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B89" s="1">
+        <v>11394.74</v>
+      </c>
+      <c r="C89" s="1">
+        <v>1.4297038895859473</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B90" s="1">
+        <v>11060.08</v>
+      </c>
+      <c r="C90" s="1">
+        <v>1.7115567935623646</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B91" s="1">
+        <v>10341.44</v>
+      </c>
+      <c r="C91" s="1">
+        <v>1.4146976744186046</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B92" s="1">
+        <v>9401.85</v>
+      </c>
+      <c r="C92" s="1">
+        <v>1.1117240156083719</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B93" s="1">
+        <v>9257.56</v>
+      </c>
+      <c r="C93" s="1">
+        <v>0.81299376481953101</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B94" s="1">
+        <v>8675.94</v>
+      </c>
+      <c r="C94" s="1">
+        <v>0.7920339601971883</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="B95" s="1">
+        <v>7228.42</v>
+      </c>
+      <c r="C95" s="1">
+        <v>1.1289114477588631</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B96" s="1">
+        <v>6070.76</v>
+      </c>
+      <c r="C96" s="1">
+        <v>0.80194980184940556</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B97" s="1">
+        <v>5639.28</v>
+      </c>
+      <c r="C97" s="1">
+        <v>0.53651222528779374</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B98" s="1">
+        <v>5526.74</v>
+      </c>
+      <c r="C98" s="1">
+        <v>0.63141094481891924</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B99" s="1">
+        <v>4534.01</v>
+      </c>
+      <c r="C99" s="1">
+        <v>0.88365036055349844</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B100" s="1">
+        <v>2640.79</v>
+      </c>
+      <c r="C100" s="1">
+        <v>0.41804495804970715</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B101" s="1">
+        <v>2608.64</v>
+      </c>
+      <c r="C101" s="1">
+        <v>0.64746587242491926</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B102" s="1">
+        <v>324</v>
+      </c>
+      <c r="C102" s="1">
+        <v>4.3542534605563767E-2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="B103" s="1">
+        <v>21198161.640000008</v>
+      </c>
+      <c r="C103" s="1">
+        <v>412.38484691779973</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D492B738-6239-4F44-A0E3-4FF998BF97B5}">
   <dimension ref="A1:Q100"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1709,11 +7027,11 @@
         <v>86397461.790000007</v>
       </c>
       <c r="E2" s="2">
-        <f>C2/D2*100</f>
+        <f t="shared" ref="E2:E33" si="0">C2/D2*100</f>
         <v>5.7859581710288106</v>
       </c>
       <c r="F2" s="1">
-        <f>C2/B2</f>
+        <f t="shared" ref="F2:F33" si="1">C2/B2</f>
         <v>11.608120471855843</v>
       </c>
       <c r="H2">
@@ -1737,11 +7055,11 @@
         <v>2779364.89</v>
       </c>
       <c r="P2" s="9">
-        <f>N2/O2*100</f>
+        <f t="shared" ref="P2:P33" si="2">N2/O2*100</f>
         <v>5.0124170633816991</v>
       </c>
       <c r="Q2" s="8">
-        <f>N2/M2</f>
+        <f t="shared" ref="Q2:Q33" si="3">N2/M2</f>
         <v>4.1824539914137313</v>
       </c>
     </row>
@@ -1759,11 +7077,11 @@
         <v>27902848.670000002</v>
       </c>
       <c r="E3" s="2">
-        <f>C3/D3*100</f>
+        <f t="shared" si="0"/>
         <v>6.2426402787783886</v>
       </c>
       <c r="F3" s="1">
-        <f>C3/B3</f>
+        <f t="shared" si="1"/>
         <v>10.542502723575268</v>
       </c>
       <c r="L3" s="7" t="s">
@@ -1779,11 +7097,11 @@
         <v>1337091.6299999999</v>
       </c>
       <c r="P3" s="9">
-        <f>N3/O3*100</f>
+        <f t="shared" si="2"/>
         <v>3.9182654968829631</v>
       </c>
       <c r="Q3" s="8">
-        <f>N3/M3</f>
+        <f t="shared" si="3"/>
         <v>4.1798946864528483</v>
       </c>
     </row>
@@ -1801,11 +7119,11 @@
         <v>34460047.490000002</v>
       </c>
       <c r="E4" s="2">
-        <f>C4/D4*100</f>
+        <f t="shared" si="0"/>
         <v>4.9100815676211944</v>
       </c>
       <c r="F4" s="1">
-        <f>C4/B4</f>
+        <f t="shared" si="1"/>
         <v>8.0104553416719533</v>
       </c>
       <c r="L4" s="7" t="s">
@@ -1821,11 +7139,11 @@
         <v>1527535.95</v>
       </c>
       <c r="P4" s="9">
-        <f>N4/O4*100</f>
+        <f t="shared" si="2"/>
         <v>3.7619356847215282</v>
       </c>
       <c r="Q4" s="8">
-        <f>N4/M4</f>
+        <f t="shared" si="3"/>
         <v>4.1175781026081975</v>
       </c>
     </row>
@@ -1843,11 +7161,11 @@
         <v>24200402.25</v>
       </c>
       <c r="E5" s="2">
-        <f>C5/D5*100</f>
+        <f t="shared" si="0"/>
         <v>6.0811961916872681</v>
       </c>
       <c r="F5" s="1">
-        <f>C5/B5</f>
+        <f t="shared" si="1"/>
         <v>11.244280649745573</v>
       </c>
       <c r="L5" s="7" t="s">
@@ -1863,11 +7181,11 @@
         <v>1598830.32</v>
       </c>
       <c r="P5" s="9">
-        <f>N5/O5*100</f>
+        <f t="shared" si="2"/>
         <v>5.2340557314424707</v>
       </c>
       <c r="Q5" s="8">
-        <f>N5/M5</f>
+        <f t="shared" si="3"/>
         <v>4.0548342862680489</v>
       </c>
     </row>
@@ -1885,11 +7203,11 @@
         <v>22967283.289999999</v>
       </c>
       <c r="E6" s="2">
-        <f>C6/D6*100</f>
+        <f t="shared" si="0"/>
         <v>5.092748564255638</v>
       </c>
       <c r="F6" s="1">
-        <f>C6/B6</f>
+        <f t="shared" si="1"/>
         <v>8.9226179723853836</v>
       </c>
       <c r="L6" s="7" t="s">
@@ -1905,11 +7223,11 @@
         <v>2441399.88</v>
       </c>
       <c r="P6" s="9">
-        <f>N6/O6*100</f>
+        <f t="shared" si="2"/>
         <v>4.2493640984368364</v>
       </c>
       <c r="Q6" s="8">
-        <f>N6/M6</f>
+        <f t="shared" si="3"/>
         <v>3.9437379305101499</v>
       </c>
     </row>
@@ -1927,11 +7245,11 @@
         <v>11879190.380000001</v>
       </c>
       <c r="E7" s="2">
-        <f>C7/D7*100</f>
+        <f t="shared" si="0"/>
         <v>6.7990282516206282</v>
       </c>
       <c r="F7" s="1">
-        <f>C7/B7</f>
+        <f t="shared" si="1"/>
         <v>8.6240644720404038</v>
       </c>
       <c r="L7" s="7" t="s">
@@ -1947,11 +7265,11 @@
         <v>2268583.98</v>
       </c>
       <c r="P7" s="9">
-        <f>N7/O7*100</f>
+        <f t="shared" si="2"/>
         <v>4.3384490443241166</v>
       </c>
       <c r="Q7" s="8">
-        <f>N7/M7</f>
+        <f t="shared" si="3"/>
         <v>3.9390602737533018</v>
       </c>
     </row>
@@ -1969,11 +7287,11 @@
         <v>14177698.300000001</v>
       </c>
       <c r="E8" s="2">
-        <f>C8/D8*100</f>
+        <f t="shared" si="0"/>
         <v>5.6106169927455705</v>
       </c>
       <c r="F8" s="1">
-        <f>C8/B8</f>
+        <f t="shared" si="1"/>
         <v>8.5387873290538661</v>
       </c>
       <c r="L8" s="7" t="s">
@@ -1989,11 +7307,11 @@
         <v>2012519.27</v>
       </c>
       <c r="P8" s="9">
-        <f>N8/O8*100</f>
+        <f t="shared" si="2"/>
         <v>3.6989832152017108</v>
       </c>
       <c r="Q8" s="8">
-        <f>N8/M8</f>
+        <f t="shared" si="3"/>
         <v>3.9358543935708998</v>
       </c>
     </row>
@@ -2011,11 +7329,11 @@
         <v>13242016.16</v>
       </c>
       <c r="E9" s="2">
-        <f>C9/D9*100</f>
+        <f t="shared" si="0"/>
         <v>5.602493918116469</v>
       </c>
       <c r="F9" s="1">
-        <f>C9/B9</f>
+        <f t="shared" si="1"/>
         <v>7.2611199741612182</v>
       </c>
       <c r="L9" s="7" t="s">
@@ -2031,11 +7349,11 @@
         <v>1571213.86</v>
       </c>
       <c r="P9" s="9">
-        <f>N9/O9*100</f>
+        <f t="shared" si="2"/>
         <v>3.9933201709409563</v>
       </c>
       <c r="Q9" s="8">
-        <f>N9/M9</f>
+        <f t="shared" si="3"/>
         <v>3.84859228362878</v>
       </c>
     </row>
@@ -2053,11 +7371,11 @@
         <v>12267027.18</v>
       </c>
       <c r="E10" s="2">
-        <f>C10/D10*100</f>
+        <f t="shared" si="0"/>
         <v>5.8085589894323526</v>
       </c>
       <c r="F10" s="1">
-        <f>C10/B10</f>
+        <f t="shared" si="1"/>
         <v>7.9575786781622035</v>
       </c>
       <c r="L10" s="7" t="s">
@@ -2073,11 +7391,11 @@
         <v>2076294.71</v>
       </c>
       <c r="P10" s="9">
-        <f>N10/O10*100</f>
+        <f t="shared" si="2"/>
         <v>6.2457087317821083</v>
       </c>
       <c r="Q10" s="8">
-        <f>N10/M10</f>
+        <f t="shared" si="3"/>
         <v>3.8475943508188939</v>
       </c>
     </row>
@@ -2095,11 +7413,11 @@
         <v>7898228.4199999999</v>
       </c>
       <c r="E11" s="2">
-        <f>C11/D11*100</f>
+        <f t="shared" si="0"/>
         <v>7.8972490643667665</v>
       </c>
       <c r="F11" s="1">
-        <f>C11/B11</f>
+        <f t="shared" si="1"/>
         <v>9.4313566190368192</v>
       </c>
       <c r="L11" s="7" t="s">
@@ -2115,11 +7433,11 @@
         <v>790327.5</v>
       </c>
       <c r="P11" s="9">
-        <f>N11/O11*100</f>
+        <f t="shared" si="2"/>
         <v>4.416815813697486</v>
       </c>
       <c r="Q11" s="8">
-        <f>N11/M11</f>
+        <f t="shared" si="3"/>
         <v>3.7766212268743913</v>
       </c>
     </row>
@@ -2137,11 +7455,11 @@
         <v>7998958.9199999999</v>
       </c>
       <c r="E12" s="2">
-        <f>C12/D12*100</f>
+        <f t="shared" si="0"/>
         <v>5.3121477963534787</v>
       </c>
       <c r="F12" s="1">
-        <f>C12/B12</f>
+        <f t="shared" si="1"/>
         <v>9.6241652510701918</v>
       </c>
       <c r="L12" s="7" t="s">
@@ -2157,11 +7475,11 @@
         <v>339968.23</v>
       </c>
       <c r="P12" s="9">
-        <f>N12/O12*100</f>
+        <f t="shared" si="2"/>
         <v>8.1735578645098705</v>
       </c>
       <c r="Q12" s="8">
-        <f>N12/M12</f>
+        <f t="shared" si="3"/>
         <v>3.6572124243221902</v>
       </c>
     </row>
@@ -2179,11 +7497,11 @@
         <v>5142111.9000000004</v>
       </c>
       <c r="E13" s="2">
-        <f>C13/D13*100</f>
+        <f t="shared" si="0"/>
         <v>6.9162804488949376</v>
       </c>
       <c r="F13" s="1">
-        <f>C13/B13</f>
+        <f t="shared" si="1"/>
         <v>21.338146037079259</v>
       </c>
       <c r="L13" s="7" t="s">
@@ -2199,11 +7517,11 @@
         <v>1618152.03</v>
       </c>
       <c r="P13" s="9">
-        <f>N13/O13*100</f>
+        <f t="shared" si="2"/>
         <v>3.5667606584530871</v>
       </c>
       <c r="Q13" s="8">
-        <f>N13/M13</f>
+        <f t="shared" si="3"/>
         <v>3.6226217675119257</v>
       </c>
     </row>
@@ -2221,11 +7539,11 @@
         <v>5168751.09</v>
       </c>
       <c r="E14" s="2">
-        <f>C14/D14*100</f>
+        <f t="shared" si="0"/>
         <v>5.4949777045657653</v>
       </c>
       <c r="F14" s="1">
-        <f>C14/B14</f>
+        <f t="shared" si="1"/>
         <v>7.0433160570365771</v>
       </c>
       <c r="L14" s="7" t="s">
@@ -2241,11 +7559,11 @@
         <v>940960.97</v>
       </c>
       <c r="P14" s="9">
-        <f>N14/O14*100</f>
+        <f t="shared" si="2"/>
         <v>3.74943713127655</v>
       </c>
       <c r="Q14" s="8">
-        <f>N14/M14</f>
+        <f t="shared" si="3"/>
         <v>3.5945736118186447</v>
       </c>
     </row>
@@ -2263,11 +7581,11 @@
         <v>4851700.7300000004</v>
       </c>
       <c r="E15" s="2">
-        <f>C15/D15*100</f>
+        <f t="shared" si="0"/>
         <v>5.8046743950754767</v>
       </c>
       <c r="F15" s="1">
-        <f>C15/B15</f>
+        <f t="shared" si="1"/>
         <v>5.733883663164753</v>
       </c>
       <c r="L15" s="7" t="s">
@@ -2283,11 +7601,11 @@
         <v>1107480.6599999999</v>
       </c>
       <c r="P15" s="9">
-        <f>N15/O15*100</f>
+        <f t="shared" si="2"/>
         <v>4.6496884198411204</v>
       </c>
       <c r="Q15" s="8">
-        <f>N15/M15</f>
+        <f t="shared" si="3"/>
         <v>3.5934682484298675</v>
       </c>
     </row>
@@ -2305,11 +7623,11 @@
         <v>4387996.29</v>
       </c>
       <c r="E16" s="2">
-        <f>C16/D16*100</f>
+        <f t="shared" si="0"/>
         <v>6.2363860840912428</v>
       </c>
       <c r="F16" s="1">
-        <f>C16/B16</f>
+        <f t="shared" si="1"/>
         <v>6.4019742659960235</v>
       </c>
       <c r="L16" s="7" t="s">
@@ -2325,11 +7643,11 @@
         <v>746083.11</v>
       </c>
       <c r="P16" s="9">
-        <f>N16/O16*100</f>
+        <f t="shared" si="2"/>
         <v>4.9800993350459306</v>
       </c>
       <c r="Q16" s="8">
-        <f>N16/M16</f>
+        <f t="shared" si="3"/>
         <v>3.5899207729468601</v>
       </c>
     </row>
@@ -2347,11 +7665,11 @@
         <v>4881120.76</v>
       </c>
       <c r="E17" s="2">
-        <f>C17/D17*100</f>
+        <f t="shared" si="0"/>
         <v>4.9990867261395104</v>
       </c>
       <c r="F17" s="1">
-        <f>C17/B17</f>
+        <f t="shared" si="1"/>
         <v>6.804178796497685</v>
       </c>
       <c r="L17" s="7" t="s">
@@ -2367,11 +7685,11 @@
         <v>840077.29</v>
       </c>
       <c r="P17" s="9">
-        <f>N17/O17*100</f>
+        <f t="shared" si="2"/>
         <v>4.3970966052421199</v>
       </c>
       <c r="Q17" s="8">
-        <f>N17/M17</f>
+        <f t="shared" si="3"/>
         <v>3.5856154144826249</v>
       </c>
     </row>
@@ -2389,11 +7707,11 @@
         <v>3183557.2</v>
       </c>
       <c r="E18" s="2">
-        <f>C18/D18*100</f>
+        <f t="shared" si="0"/>
         <v>7.4683310229198954</v>
       </c>
       <c r="F18" s="1">
-        <f>C18/B18</f>
+        <f t="shared" si="1"/>
         <v>11.421915353574173</v>
       </c>
       <c r="L18" s="7" t="s">
@@ -2409,11 +7727,11 @@
         <v>1089064.58</v>
       </c>
       <c r="P18" s="9">
-        <f>N18/O18*100</f>
+        <f t="shared" si="2"/>
         <v>4.2159767972621056</v>
       </c>
       <c r="Q18" s="8">
-        <f>N18/M18</f>
+        <f t="shared" si="3"/>
         <v>3.5636999379074821</v>
       </c>
     </row>
@@ -2431,11 +7749,11 @@
         <v>4323049.3</v>
       </c>
       <c r="E19" s="2">
-        <f>C19/D19*100</f>
+        <f t="shared" si="0"/>
         <v>5.3059408783517688</v>
       </c>
       <c r="F19" s="1">
-        <f>C19/B19</f>
+        <f t="shared" si="1"/>
         <v>6.03421040170468</v>
       </c>
       <c r="L19" s="7" t="s">
@@ -2451,11 +7769,11 @@
         <v>702357.9</v>
       </c>
       <c r="P19" s="9">
-        <f>N19/O19*100</f>
+        <f t="shared" si="2"/>
         <v>5.3860346697887209</v>
       </c>
       <c r="Q19" s="8">
-        <f>N19/M19</f>
+        <f t="shared" si="3"/>
         <v>3.5420636704119848</v>
       </c>
     </row>
@@ -2473,11 +7791,11 @@
         <v>4092699.9</v>
       </c>
       <c r="E20" s="2">
-        <f>C20/D20*100</f>
+        <f t="shared" si="0"/>
         <v>4.1970795366647824</v>
       </c>
       <c r="F20" s="1">
-        <f>C20/B20</f>
+        <f t="shared" si="1"/>
         <v>4.2258873745325722</v>
       </c>
       <c r="L20" s="7" t="s">
@@ -2493,11 +7811,11 @@
         <v>991451.14</v>
       </c>
       <c r="P20" s="9">
-        <f>N20/O20*100</f>
+        <f t="shared" si="2"/>
         <v>4.7257134627935367</v>
       </c>
       <c r="Q20" s="8">
-        <f>N20/M20</f>
+        <f t="shared" si="3"/>
         <v>3.5416992969990173</v>
       </c>
     </row>
@@ -2515,11 +7833,11 @@
         <v>3658972.86</v>
       </c>
       <c r="E21" s="2">
-        <f>C21/D21*100</f>
+        <f t="shared" si="0"/>
         <v>4.1200772940414767</v>
       </c>
       <c r="F21" s="1">
-        <f>C21/B21</f>
+        <f t="shared" si="1"/>
         <v>4.2316494035087722</v>
       </c>
       <c r="L21" s="7" t="s">
@@ -2535,11 +7853,11 @@
         <v>1776809.53</v>
       </c>
       <c r="P21" s="9">
-        <f>N21/O21*100</f>
+        <f t="shared" si="2"/>
         <v>2.7894070334032932</v>
       </c>
       <c r="Q21" s="8">
-        <f>N21/M21</f>
+        <f t="shared" si="3"/>
         <v>3.4423149048478954</v>
       </c>
     </row>
@@ -2557,11 +7875,11 @@
         <v>2779364.89</v>
       </c>
       <c r="E22" s="6">
-        <f>C22/D22*100</f>
+        <f t="shared" si="0"/>
         <v>5.0124170633816991</v>
       </c>
       <c r="F22" s="5">
-        <f>C22/B22</f>
+        <f t="shared" si="1"/>
         <v>4.1824539914137313</v>
       </c>
       <c r="L22" s="7" t="s">
@@ -2577,11 +7895,11 @@
         <v>603641</v>
       </c>
       <c r="P22" s="9">
-        <f>N22/O22*100</f>
+        <f t="shared" si="2"/>
         <v>4.0114057858892949</v>
       </c>
       <c r="Q22" s="8">
-        <f>N22/M22</f>
+        <f t="shared" si="3"/>
         <v>3.4157836084073918</v>
       </c>
     </row>
@@ -2599,11 +7917,11 @@
         <v>2076294.71</v>
       </c>
       <c r="E23" s="6">
-        <f>C23/D23*100</f>
+        <f t="shared" si="0"/>
         <v>6.2457087317821083</v>
       </c>
       <c r="F23" s="5">
-        <f>C23/B23</f>
+        <f t="shared" si="1"/>
         <v>3.8475943508188939</v>
       </c>
       <c r="L23" s="7" t="s">
@@ -2619,11 +7937,11 @@
         <v>1024856.07</v>
       </c>
       <c r="P23" s="9">
-        <f>N23/O23*100</f>
+        <f t="shared" si="2"/>
         <v>3.8540241070143635</v>
       </c>
       <c r="Q23" s="8">
-        <f>N23/M23</f>
+        <f t="shared" si="3"/>
         <v>3.410603574820827</v>
       </c>
     </row>
@@ -2641,11 +7959,11 @@
         <v>2432925.21</v>
       </c>
       <c r="E24" s="2">
-        <f>C24/D24*100</f>
+        <f t="shared" si="0"/>
         <v>5.1979065973836489</v>
       </c>
       <c r="F24" s="1">
-        <f>C24/B24</f>
+        <f t="shared" si="1"/>
         <v>6.2419141164856855</v>
       </c>
       <c r="L24" s="7" t="s">
@@ -2661,11 +7979,11 @@
         <v>1277554.19</v>
       </c>
       <c r="P24" s="9">
-        <f>N24/O24*100</f>
+        <f t="shared" si="2"/>
         <v>4.6951973129218105</v>
       </c>
       <c r="Q24" s="8">
-        <f>N24/M24</f>
+        <f t="shared" si="3"/>
         <v>3.3766995046160777</v>
       </c>
     </row>
@@ -2683,11 +8001,11 @@
         <v>2567270.44</v>
       </c>
       <c r="E25" s="2">
-        <f>C25/D25*100</f>
+        <f t="shared" si="0"/>
         <v>4.8316062876492278</v>
       </c>
       <c r="F25" s="1">
-        <f>C25/B25</f>
+        <f t="shared" si="1"/>
         <v>7.0742785445420324</v>
       </c>
       <c r="L25" s="7" t="s">
@@ -2703,11 +8021,11 @@
         <v>1720246.48</v>
       </c>
       <c r="P25" s="9">
-        <f>N25/O25*100</f>
+        <f t="shared" si="2"/>
         <v>3.8917905531770076</v>
       </c>
       <c r="Q25" s="8">
-        <f>N25/M25</f>
+        <f t="shared" si="3"/>
         <v>3.3730547158403867</v>
       </c>
     </row>
@@ -2725,11 +8043,11 @@
         <v>2507674.79</v>
       </c>
       <c r="E26" s="2">
-        <f>C26/D26*100</f>
+        <f t="shared" si="0"/>
         <v>4.8381536746238138</v>
       </c>
       <c r="F26" s="1">
-        <f>C26/B26</f>
+        <f t="shared" si="1"/>
         <v>4.9977409787444387</v>
       </c>
       <c r="L26" s="7" t="s">
@@ -2745,11 +8063,11 @@
         <v>1949162.4</v>
       </c>
       <c r="P26" s="9">
-        <f>N26/O26*100</f>
+        <f t="shared" si="2"/>
         <v>3.2442253144222359</v>
       </c>
       <c r="Q26" s="8">
-        <f>N26/M26</f>
+        <f t="shared" si="3"/>
         <v>3.0172354232274072</v>
       </c>
     </row>
@@ -2767,11 +8085,11 @@
         <v>3028648.21</v>
       </c>
       <c r="E27" s="6">
-        <f>C27/D27*100</f>
+        <f t="shared" si="0"/>
         <v>3.732094722219323</v>
       </c>
       <c r="F27" s="5">
-        <f>C27/B27</f>
+        <f t="shared" si="1"/>
         <v>2.4452573282855599</v>
       </c>
       <c r="L27" s="7" t="s">
@@ -2787,11 +8105,11 @@
         <v>1550328.8</v>
       </c>
       <c r="P27" s="9">
-        <f>N27/O27*100</f>
+        <f t="shared" si="2"/>
         <v>3.9014156222860592</v>
       </c>
       <c r="Q27" s="8">
-        <f>N27/M27</f>
+        <f t="shared" si="3"/>
         <v>3.002470588235294</v>
       </c>
     </row>
@@ -2809,11 +8127,11 @@
         <v>1956732.65</v>
       </c>
       <c r="E28" s="2">
-        <f>C28/D28*100</f>
+        <f t="shared" si="0"/>
         <v>5.6662349861643087</v>
       </c>
       <c r="F28" s="1">
-        <f>C28/B28</f>
+        <f t="shared" si="1"/>
         <v>5.2656283244680857</v>
       </c>
       <c r="L28" s="7" t="s">
@@ -2829,11 +8147,11 @@
         <v>241821.88</v>
       </c>
       <c r="P28" s="9">
-        <f>N28/O28*100</f>
+        <f t="shared" si="2"/>
         <v>7.5372666857109856</v>
       </c>
       <c r="Q28" s="8">
-        <f>N28/M28</f>
+        <f t="shared" si="3"/>
         <v>2.9787154763850299</v>
       </c>
     </row>
@@ -2851,11 +8169,11 @@
         <v>2522531.13</v>
       </c>
       <c r="E29" s="2">
-        <f>C29/D29*100</f>
+        <f t="shared" si="0"/>
         <v>4.3218669812808219</v>
       </c>
       <c r="F29" s="1">
-        <f>C29/B29</f>
+        <f t="shared" si="1"/>
         <v>7.01411825258959</v>
       </c>
       <c r="L29" s="7" t="s">
@@ -2871,11 +8189,11 @@
         <v>1668008.23</v>
       </c>
       <c r="P29" s="9">
-        <f>N29/O29*100</f>
+        <f t="shared" si="2"/>
         <v>3.7010153121366796</v>
       </c>
       <c r="Q29" s="8">
-        <f>N29/M29</f>
+        <f t="shared" si="3"/>
         <v>2.9565727969348656</v>
       </c>
     </row>
@@ -2893,11 +8211,11 @@
         <v>2441399.88</v>
       </c>
       <c r="E30" s="6">
-        <f>C30/D30*100</f>
+        <f t="shared" si="0"/>
         <v>4.2493640984368364</v>
       </c>
       <c r="F30" s="5">
-        <f>C30/B30</f>
+        <f t="shared" si="1"/>
         <v>3.9437379305101499</v>
       </c>
       <c r="L30" s="7" t="s">
@@ -2913,11 +8231,11 @@
         <v>644715.72</v>
       </c>
       <c r="P30" s="9">
-        <f>N30/O30*100</f>
+        <f t="shared" si="2"/>
         <v>4.9196613353867038</v>
       </c>
       <c r="Q30" s="8">
-        <f>N30/M30</f>
+        <f t="shared" si="3"/>
         <v>2.9433769487750556</v>
       </c>
     </row>
@@ -2935,11 +8253,11 @@
         <v>2047974.45</v>
       </c>
       <c r="E31" s="2">
-        <f>C31/D31*100</f>
+        <f t="shared" si="0"/>
         <v>4.948179895506021</v>
       </c>
       <c r="F31" s="1">
-        <f>C31/B31</f>
+        <f t="shared" si="1"/>
         <v>4.6690683744931816</v>
       </c>
       <c r="L31" s="7" t="s">
@@ -2955,11 +8273,11 @@
         <v>482178.34</v>
       </c>
       <c r="P31" s="9">
-        <f>N31/O31*100</f>
+        <f t="shared" si="2"/>
         <v>5.6538168014763999</v>
       </c>
       <c r="Q31" s="8">
-        <f>N31/M31</f>
+        <f t="shared" si="3"/>
         <v>2.8191809720785934</v>
       </c>
     </row>
@@ -2977,11 +8295,11 @@
         <v>2226471.23</v>
       </c>
       <c r="E32" s="2">
-        <f>C32/D32*100</f>
+        <f t="shared" si="0"/>
         <v>4.5404795102607274</v>
       </c>
       <c r="F32" s="1">
-        <f>C32/B32</f>
+        <f t="shared" si="1"/>
         <v>6.1811354325894223</v>
       </c>
       <c r="L32" s="7" t="s">
@@ -2997,11 +8315,11 @@
         <v>845731.43</v>
       </c>
       <c r="P32" s="9">
-        <f>N32/O32*100</f>
+        <f t="shared" si="2"/>
         <v>3.0892537599081544</v>
       </c>
       <c r="Q32" s="8">
-        <f>N32/M32</f>
+        <f t="shared" si="3"/>
         <v>2.8135677363773421</v>
       </c>
     </row>
@@ -3019,11 +8337,11 @@
         <v>2544580.83</v>
       </c>
       <c r="E33" s="6">
-        <f>C33/D33*100</f>
+        <f t="shared" si="0"/>
         <v>3.9128043733631364</v>
       </c>
       <c r="F33" s="5">
-        <f>C33/B33</f>
+        <f t="shared" si="1"/>
         <v>2.7024719070625918</v>
       </c>
       <c r="L33" s="7" t="s">
@@ -3039,11 +8357,11 @@
         <v>603088.67000000004</v>
       </c>
       <c r="P33" s="9">
-        <f>N33/O33*100</f>
+        <f t="shared" si="2"/>
         <v>3.5675583160930544</v>
       </c>
       <c r="Q33" s="8">
-        <f>N33/M33</f>
+        <f t="shared" si="3"/>
         <v>2.8007732361364228</v>
       </c>
     </row>
@@ -3061,11 +8379,11 @@
         <v>2268583.98</v>
       </c>
       <c r="E34" s="6">
-        <f>C34/D34*100</f>
+        <f t="shared" ref="E34:E65" si="4">C34/D34*100</f>
         <v>4.3384490443241166</v>
       </c>
       <c r="F34" s="5">
-        <f>C34/B34</f>
+        <f t="shared" ref="F34:F65" si="5">C34/B34</f>
         <v>3.9390602737533018</v>
       </c>
       <c r="L34" s="7" t="s">
@@ -3081,11 +8399,11 @@
         <v>1378251.77</v>
       </c>
       <c r="P34" s="9">
-        <f>N34/O34*100</f>
+        <f t="shared" ref="P34:P65" si="6">N34/O34*100</f>
         <v>4.5333197721922751</v>
       </c>
       <c r="Q34" s="8">
-        <f>N34/M34</f>
+        <f t="shared" ref="Q34:Q67" si="7">N34/M34</f>
         <v>2.7916786560028592</v>
       </c>
     </row>
@@ -3103,11 +8421,11 @@
         <v>2140888</v>
       </c>
       <c r="E35" s="2">
-        <f>C35/D35*100</f>
+        <f t="shared" si="4"/>
         <v>4.2901669774411362</v>
       </c>
       <c r="F35" s="1">
-        <f>C35/B35</f>
+        <f t="shared" si="5"/>
         <v>5.5107499850002997</v>
       </c>
       <c r="L35" s="7" t="s">
@@ -3123,11 +8441,11 @@
         <v>1120768.6100000001</v>
       </c>
       <c r="P35" s="9">
-        <f>N35/O35*100</f>
+        <f t="shared" si="6"/>
         <v>4.1164759244997056</v>
       </c>
       <c r="Q35" s="8">
-        <f>N35/M35</f>
+        <f t="shared" si="7"/>
         <v>2.739189574303865</v>
       </c>
     </row>
@@ -3145,11 +8463,11 @@
         <v>1598830.32</v>
       </c>
       <c r="E36" s="6">
-        <f>C36/D36*100</f>
+        <f t="shared" si="4"/>
         <v>5.2340557314424707</v>
       </c>
       <c r="F36" s="5">
-        <f>C36/B36</f>
+        <f t="shared" si="5"/>
         <v>4.0548342862680489</v>
       </c>
       <c r="L36" s="7" t="s">
@@ -3165,11 +8483,11 @@
         <v>2544580.83</v>
       </c>
       <c r="P36" s="9">
-        <f>N36/O36*100</f>
+        <f t="shared" si="6"/>
         <v>3.9128043733631364</v>
       </c>
       <c r="Q36" s="8">
-        <f>N36/M36</f>
+        <f t="shared" si="7"/>
         <v>2.7024719070625918</v>
       </c>
     </row>
@@ -3187,11 +8505,11 @@
         <v>1971876.55</v>
       </c>
       <c r="E37" s="2">
-        <f>C37/D37*100</f>
+        <f t="shared" si="4"/>
         <v>3.8950856228803974</v>
       </c>
       <c r="F37" s="1">
-        <f>C37/B37</f>
+        <f t="shared" si="5"/>
         <v>4.4926462330369681</v>
       </c>
       <c r="L37" s="7" t="s">
@@ -3207,11 +8525,11 @@
         <v>994568.53</v>
       </c>
       <c r="P37" s="9">
-        <f>N37/O37*100</f>
+        <f t="shared" si="6"/>
         <v>4.6612615020103245</v>
       </c>
       <c r="Q37" s="8">
-        <f>N37/M37</f>
+        <f t="shared" si="7"/>
         <v>2.557197859782669</v>
       </c>
     </row>
@@ -3229,11 +8547,11 @@
         <v>2012519.27</v>
       </c>
       <c r="E38" s="6">
-        <f>C38/D38*100</f>
+        <f t="shared" si="4"/>
         <v>3.6989832152017108</v>
       </c>
       <c r="F38" s="5">
-        <f>C38/B38</f>
+        <f t="shared" si="5"/>
         <v>3.9358543935708998</v>
       </c>
       <c r="L38" s="7" t="s">
@@ -3249,11 +8567,11 @@
         <v>1244371.58</v>
       </c>
       <c r="P38" s="9">
-        <f>N38/O38*100</f>
+        <f t="shared" si="6"/>
         <v>3.2193221577754132</v>
       </c>
       <c r="Q38" s="8">
-        <f>N38/M38</f>
+        <f t="shared" si="7"/>
         <v>2.5560090601671668</v>
       </c>
     </row>
@@ -3271,11 +8589,11 @@
         <v>1163855.3500000001</v>
       </c>
       <c r="E39" s="2">
-        <f>C39/D39*100</f>
+        <f t="shared" si="4"/>
         <v>5.8744439332602623</v>
       </c>
       <c r="F39" s="1">
-        <f>C39/B39</f>
+        <f t="shared" si="5"/>
         <v>5.6193005671077501</v>
       </c>
       <c r="L39" s="7" t="s">
@@ -3291,11 +8609,11 @@
         <v>3028648.21</v>
       </c>
       <c r="P39" s="9">
-        <f>N39/O39*100</f>
+        <f t="shared" si="6"/>
         <v>3.732094722219323</v>
       </c>
       <c r="Q39" s="8">
-        <f>N39/M39</f>
+        <f t="shared" si="7"/>
         <v>2.4452573282855599</v>
       </c>
     </row>
@@ -3313,11 +8631,11 @@
         <v>1720246.48</v>
       </c>
       <c r="E40" s="6">
-        <f>C40/D40*100</f>
+        <f t="shared" si="4"/>
         <v>3.8917905531770076</v>
       </c>
       <c r="F40" s="5">
-        <f>C40/B40</f>
+        <f t="shared" si="5"/>
         <v>3.3730547158403867</v>
       </c>
       <c r="L40" s="7" t="s">
@@ -3333,11 +8651,11 @@
         <v>548905.25</v>
       </c>
       <c r="P40" s="9">
-        <f>N40/O40*100</f>
+        <f t="shared" si="6"/>
         <v>4.1386614538665834</v>
       </c>
       <c r="Q40" s="8">
-        <f>N40/M40</f>
+        <f t="shared" si="7"/>
         <v>2.43330441302485</v>
       </c>
     </row>
@@ -3355,11 +8673,11 @@
         <v>1024059.83</v>
       </c>
       <c r="E41" s="2">
-        <f>C41/D41*100</f>
+        <f t="shared" si="4"/>
         <v>6.3510439619528878</v>
       </c>
       <c r="F41" s="1">
-        <f>C41/B41</f>
+        <f t="shared" si="5"/>
         <v>5.985504325418737</v>
       </c>
       <c r="L41" s="7" t="s">
@@ -3375,11 +8693,11 @@
         <v>839109.2</v>
       </c>
       <c r="P41" s="9">
-        <f>N41/O41*100</f>
+        <f t="shared" si="6"/>
         <v>3.0593062261741379</v>
       </c>
       <c r="Q41" s="8">
-        <f>N41/M41</f>
+        <f t="shared" si="7"/>
         <v>2.3902160148975788</v>
       </c>
     </row>
@@ -3397,11 +8715,11 @@
         <v>1949162.4</v>
       </c>
       <c r="E42" s="6">
-        <f>C42/D42*100</f>
+        <f t="shared" si="4"/>
         <v>3.2442253144222359</v>
       </c>
       <c r="F42" s="5">
-        <f>C42/B42</f>
+        <f t="shared" si="5"/>
         <v>3.0172354232274072</v>
       </c>
       <c r="L42" s="7" t="s">
@@ -3417,11 +8735,11 @@
         <v>981007.93</v>
       </c>
       <c r="P42" s="9">
-        <f>N42/O42*100</f>
+        <f t="shared" si="6"/>
         <v>2.898710512972102</v>
       </c>
       <c r="Q42" s="8">
-        <f>N42/M42</f>
+        <f t="shared" si="7"/>
         <v>2.3555815109343938</v>
       </c>
     </row>
@@ -3439,11 +8757,11 @@
         <v>1571213.86</v>
       </c>
       <c r="E43" s="6">
-        <f>C43/D43*100</f>
+        <f t="shared" si="4"/>
         <v>3.9933201709409563</v>
       </c>
       <c r="F43" s="5">
-        <f>C43/B43</f>
+        <f t="shared" si="5"/>
         <v>3.84859228362878</v>
       </c>
       <c r="L43" s="7" t="s">
@@ -3459,11 +8777,11 @@
         <v>617724.37</v>
       </c>
       <c r="P43" s="9">
-        <f>N43/O43*100</f>
+        <f t="shared" si="6"/>
         <v>5.23422444868089</v>
       </c>
       <c r="Q43" s="8">
-        <f>N43/M43</f>
+        <f t="shared" si="7"/>
         <v>2.147093432498838</v>
       </c>
     </row>
@@ -3481,11 +8799,11 @@
         <v>1378251.77</v>
       </c>
       <c r="E44" s="6">
-        <f>C44/D44*100</f>
+        <f t="shared" si="4"/>
         <v>4.5333197721922751</v>
       </c>
       <c r="F44" s="5">
-        <f>C44/B44</f>
+        <f t="shared" si="5"/>
         <v>2.7916786560028592</v>
       </c>
       <c r="L44" s="7" t="s">
@@ -3501,11 +8819,11 @@
         <v>876011.17</v>
       </c>
       <c r="P44" s="9">
-        <f>N44/O44*100</f>
+        <f t="shared" si="6"/>
         <v>3.9347546219073894</v>
       </c>
       <c r="Q44" s="8">
-        <f>N44/M44</f>
+        <f t="shared" si="7"/>
         <v>1.9400512185512466</v>
       </c>
     </row>
@@ -3523,11 +8841,11 @@
         <v>1668008.23</v>
       </c>
       <c r="E45" s="6">
-        <f>C45/D45*100</f>
+        <f t="shared" si="4"/>
         <v>3.7010153121366796</v>
       </c>
       <c r="F45" s="5">
-        <f>C45/B45</f>
+        <f t="shared" si="5"/>
         <v>2.9565727969348656</v>
       </c>
       <c r="L45" s="7" t="s">
@@ -3543,11 +8861,11 @@
         <v>651345.05000000005</v>
       </c>
       <c r="P45" s="9">
-        <f>N45/O45*100</f>
+        <f t="shared" si="6"/>
         <v>4.2395685666145768</v>
       </c>
       <c r="Q45" s="8">
-        <f>N45/M45</f>
+        <f t="shared" si="7"/>
         <v>1.8498271704180065</v>
       </c>
     </row>
@@ -3565,11 +8883,11 @@
         <v>1550328.8</v>
       </c>
       <c r="E46" s="6">
-        <f>C46/D46*100</f>
+        <f t="shared" si="4"/>
         <v>3.9014156222860592</v>
       </c>
       <c r="F46" s="5">
-        <f>C46/B46</f>
+        <f t="shared" si="5"/>
         <v>3.002470588235294</v>
       </c>
       <c r="L46" s="7" t="s">
@@ -3585,11 +8903,11 @@
         <v>580658.38</v>
       </c>
       <c r="P46" s="9">
-        <f>N46/O46*100</f>
+        <f t="shared" si="6"/>
         <v>2.6897467664205585</v>
       </c>
       <c r="Q46" s="8">
-        <f>N46/M46</f>
+        <f t="shared" si="7"/>
         <v>1.7552528658125421</v>
       </c>
     </row>
@@ -3607,11 +8925,11 @@
         <v>1277554.19</v>
       </c>
       <c r="E47" s="6">
-        <f>C47/D47*100</f>
+        <f t="shared" si="4"/>
         <v>4.6951973129218105</v>
       </c>
       <c r="F47" s="5">
-        <f>C47/B47</f>
+        <f t="shared" si="5"/>
         <v>3.3766995046160777</v>
       </c>
       <c r="L47" s="7" t="s">
@@ -3627,11 +8945,11 @@
         <v>399807.53</v>
       </c>
       <c r="P47" s="9">
-        <f>N47/O47*100</f>
+        <f t="shared" si="6"/>
         <v>4.9334138354022494</v>
       </c>
       <c r="Q47" s="8">
-        <f>N47/M47</f>
+        <f t="shared" si="7"/>
         <v>1.739190547570761</v>
       </c>
     </row>
@@ -3649,11 +8967,11 @@
         <v>1618152.03</v>
       </c>
       <c r="E48" s="6">
-        <f>C48/D48*100</f>
+        <f t="shared" si="4"/>
         <v>3.5667606584530871</v>
       </c>
       <c r="F48" s="5">
-        <f>C48/B48</f>
+        <f t="shared" si="5"/>
         <v>3.6226217675119257</v>
       </c>
       <c r="L48" s="7" t="s">
@@ -3669,11 +8987,11 @@
         <v>344176.87</v>
       </c>
       <c r="P48" s="9">
-        <f>N48/O48*100</f>
+        <f t="shared" si="6"/>
         <v>3.2134872979697908</v>
       </c>
       <c r="Q48" s="8">
-        <f>N48/M48</f>
+        <f t="shared" si="7"/>
         <v>1.7115567935623646</v>
       </c>
     </row>
@@ -3691,11 +9009,11 @@
         <v>1527535.95</v>
       </c>
       <c r="E49" s="6">
-        <f>C49/D49*100</f>
+        <f t="shared" si="4"/>
         <v>3.7619356847215282</v>
       </c>
       <c r="F49" s="5">
-        <f>C49/B49</f>
+        <f t="shared" si="5"/>
         <v>4.1175781026081975</v>
       </c>
       <c r="L49" s="7" t="s">
@@ -3711,11 +9029,11 @@
         <v>848829.42</v>
       </c>
       <c r="P49" s="9">
-        <f>N49/O49*100</f>
+        <f t="shared" si="6"/>
         <v>3.0861442102230621</v>
       </c>
       <c r="Q49" s="8">
-        <f>N49/M49</f>
+        <f t="shared" si="7"/>
         <v>1.6707761974615727</v>
       </c>
     </row>
@@ -3733,11 +9051,11 @@
         <v>1337091.6299999999</v>
       </c>
       <c r="E50" s="6">
-        <f>C50/D50*100</f>
+        <f t="shared" si="4"/>
         <v>3.9182654968829631</v>
       </c>
       <c r="F50" s="5">
-        <f>C50/B50</f>
+        <f t="shared" si="5"/>
         <v>4.1798946864528483</v>
       </c>
       <c r="L50" s="7" t="s">
@@ -3753,11 +9071,11 @@
         <v>783200.87</v>
       </c>
       <c r="P50" s="9">
-        <f>N50/O50*100</f>
+        <f t="shared" si="6"/>
         <v>3.4653957930358277</v>
       </c>
       <c r="Q50" s="8">
-        <f>N50/M50</f>
+        <f t="shared" si="7"/>
         <v>1.4671609276177089</v>
       </c>
     </row>
@@ -3775,11 +9093,11 @@
         <v>1107480.6599999999</v>
       </c>
       <c r="E51" s="6">
-        <f>C51/D51*100</f>
+        <f t="shared" si="4"/>
         <v>4.6496884198411204</v>
       </c>
       <c r="F51" s="5">
-        <f>C51/B51</f>
+        <f t="shared" si="5"/>
         <v>3.5934682484298675</v>
       </c>
       <c r="L51" s="7" t="s">
@@ -3795,11 +9113,11 @@
         <v>417543.16</v>
       </c>
       <c r="P51" s="9">
-        <f>N51/O51*100</f>
+        <f t="shared" si="6"/>
         <v>2.7289969257309834</v>
       </c>
       <c r="Q51" s="8">
-        <f>N51/M51</f>
+        <f t="shared" si="7"/>
         <v>1.4297038895859473</v>
       </c>
     </row>
@@ -3817,11 +9135,11 @@
         <v>1776809.53</v>
       </c>
       <c r="E52" s="6">
-        <f>C52/D52*100</f>
+        <f t="shared" si="4"/>
         <v>2.7894070334032932</v>
       </c>
       <c r="F52" s="5">
-        <f>C52/B52</f>
+        <f t="shared" si="5"/>
         <v>3.4423149048478954</v>
       </c>
       <c r="L52" s="7" t="s">
@@ -3837,11 +9155,11 @@
         <v>500771.13</v>
       </c>
       <c r="P52" s="9">
-        <f>N52/O52*100</f>
+        <f t="shared" si="6"/>
         <v>2.065103074132888</v>
       </c>
       <c r="Q52" s="8">
-        <f>N52/M52</f>
+        <f t="shared" si="7"/>
         <v>1.4146976744186046</v>
       </c>
     </row>
@@ -3859,11 +9177,11 @@
         <v>991451.14</v>
       </c>
       <c r="E53" s="6">
-        <f>C53/D53*100</f>
+        <f t="shared" si="4"/>
         <v>4.7257134627935367</v>
       </c>
       <c r="F53" s="5">
-        <f>C53/B53</f>
+        <f t="shared" si="5"/>
         <v>3.5416992969990173</v>
       </c>
       <c r="L53" s="7" t="s">
@@ -3879,11 +9197,11 @@
         <v>994344.98</v>
       </c>
       <c r="P53" s="9">
-        <f>N53/O53*100</f>
+        <f t="shared" si="6"/>
         <v>3.5659947717541653</v>
       </c>
       <c r="Q53" s="8">
-        <f>N53/M53</f>
+        <f t="shared" si="7"/>
         <v>1.3598055683387023</v>
       </c>
     </row>
@@ -3901,11 +9219,11 @@
         <v>994568.53</v>
       </c>
       <c r="E54" s="6">
-        <f>C54/D54*100</f>
+        <f t="shared" si="4"/>
         <v>4.6612615020103245</v>
       </c>
       <c r="F54" s="5">
-        <f>C54/B54</f>
+        <f t="shared" si="5"/>
         <v>2.557197859782669</v>
       </c>
       <c r="L54" s="7" t="s">
@@ -3921,11 +9239,11 @@
         <v>548956.25</v>
       </c>
       <c r="P54" s="9">
-        <f>N54/O54*100</f>
+        <f t="shared" si="6"/>
         <v>2.9331317386403746</v>
       </c>
       <c r="Q54" s="8">
-        <f>N54/M54</f>
+        <f t="shared" si="7"/>
         <v>1.2944456949915588</v>
       </c>
     </row>
@@ -3943,11 +9261,11 @@
         <v>1120768.6100000001</v>
       </c>
       <c r="E55" s="6">
-        <f>C55/D55*100</f>
+        <f t="shared" si="4"/>
         <v>4.1164759244997056</v>
       </c>
       <c r="F55" s="5">
-        <f>C55/B55</f>
+        <f t="shared" si="5"/>
         <v>2.739189574303865</v>
       </c>
       <c r="L55" s="7" t="s">
@@ -3963,11 +9281,11 @@
         <v>98824.4</v>
       </c>
       <c r="P55" s="9">
-        <f>N55/O55*100</f>
+        <f t="shared" si="6"/>
         <v>7.3144081825945824</v>
       </c>
       <c r="Q55" s="8">
-        <f>N55/M55</f>
+        <f t="shared" si="7"/>
         <v>1.1289114477588631</v>
       </c>
     </row>
@@ -3985,11 +9303,11 @@
         <v>1089064.58</v>
       </c>
       <c r="E56" s="6">
-        <f>C56/D56*100</f>
+        <f t="shared" si="4"/>
         <v>4.2159767972621056</v>
       </c>
       <c r="F56" s="5">
-        <f>C56/B56</f>
+        <f t="shared" si="5"/>
         <v>3.5636999379074821</v>
       </c>
       <c r="L56" s="7" t="s">
@@ -4005,11 +9323,11 @@
         <v>248492.15</v>
       </c>
       <c r="P56" s="9">
-        <f>N56/O56*100</f>
+        <f t="shared" si="6"/>
         <v>3.7835601647778412</v>
       </c>
       <c r="Q56" s="8">
-        <f>N56/M56</f>
+        <f t="shared" si="7"/>
         <v>1.1117240156083719</v>
       </c>
     </row>
@@ -4027,11 +9345,11 @@
         <v>1114317.54</v>
       </c>
       <c r="E57" s="2">
-        <f>C57/D57*100</f>
+        <f t="shared" si="4"/>
         <v>4.0304050136373153</v>
       </c>
       <c r="F57" s="1">
-        <f>C57/B57</f>
+        <f t="shared" si="5"/>
         <v>4.6949100982646881</v>
       </c>
       <c r="L57" s="7" t="s">
@@ -4047,11 +9365,11 @@
         <v>405592.83</v>
       </c>
       <c r="P57" s="9">
-        <f>N57/O57*100</f>
+        <f t="shared" si="6"/>
         <v>3.0035023055018009</v>
       </c>
       <c r="Q57" s="8">
-        <f>N57/M57</f>
+        <f t="shared" si="7"/>
         <v>0.97823737252067777</v>
       </c>
     </row>
@@ -4069,11 +9387,11 @@
         <v>941404.65</v>
       </c>
       <c r="E58" s="2">
-        <f>C58/D58*100</f>
+        <f t="shared" si="4"/>
         <v>4.7696928201916151</v>
       </c>
       <c r="F58" s="1">
-        <f>C58/B58</f>
+        <f t="shared" si="5"/>
         <v>4.7661723808512901</v>
       </c>
       <c r="L58" s="7" t="s">
@@ -4089,11 +9407,11 @@
         <v>198067.73</v>
       </c>
       <c r="P58" s="9">
-        <f>N58/O58*100</f>
+        <f t="shared" si="6"/>
         <v>2.2891209991652857</v>
       </c>
       <c r="Q58" s="8">
-        <f>N58/M58</f>
+        <f t="shared" si="7"/>
         <v>0.88365036055349844</v>
       </c>
     </row>
@@ -4111,11 +9429,11 @@
         <v>1244371.58</v>
       </c>
       <c r="E59" s="6">
-        <f>C59/D59*100</f>
+        <f t="shared" si="4"/>
         <v>3.2193221577754132</v>
       </c>
       <c r="F59" s="5">
-        <f>C59/B59</f>
+        <f t="shared" si="5"/>
         <v>2.5560090601671668</v>
       </c>
       <c r="L59" s="7" t="s">
@@ -4131,11 +9449,11 @@
         <v>399080.61</v>
       </c>
       <c r="P59" s="9">
-        <f>N59/O59*100</f>
+        <f t="shared" si="6"/>
         <v>3.2301318773668304</v>
       </c>
       <c r="Q59" s="8">
-        <f>N59/M59</f>
+        <f t="shared" si="7"/>
         <v>0.86707674715813543</v>
       </c>
     </row>
@@ -4153,11 +9471,11 @@
         <v>1024856.07</v>
       </c>
       <c r="E60" s="6">
-        <f>C60/D60*100</f>
+        <f t="shared" si="4"/>
         <v>3.8540241070143635</v>
       </c>
       <c r="F60" s="5">
-        <f>C60/B60</f>
+        <f t="shared" si="5"/>
         <v>3.410603574820827</v>
       </c>
       <c r="L60" s="7" t="s">
@@ -4173,11 +9491,11 @@
         <v>351079.49</v>
       </c>
       <c r="P60" s="9">
-        <f>N60/O60*100</f>
+        <f t="shared" si="6"/>
         <v>2.6368843135781015</v>
       </c>
       <c r="Q60" s="8">
-        <f>N60/M60</f>
+        <f t="shared" si="7"/>
         <v>0.81299376481953101</v>
       </c>
     </row>
@@ -4195,11 +9513,11 @@
         <v>702357.9</v>
       </c>
       <c r="E61" s="6">
-        <f>C61/D61*100</f>
+        <f t="shared" si="4"/>
         <v>5.3860346697887209</v>
       </c>
       <c r="F61" s="5">
-        <f>C61/B61</f>
+        <f t="shared" si="5"/>
         <v>3.5420636704119848</v>
       </c>
       <c r="L61" s="7" t="s">
@@ -4215,11 +9533,11 @@
         <v>260151.48</v>
       </c>
       <c r="P61" s="9">
-        <f>N61/O61*100</f>
+        <f t="shared" si="6"/>
         <v>2.3335481312656765</v>
       </c>
       <c r="Q61" s="8">
-        <f>N61/M61</f>
+        <f t="shared" si="7"/>
         <v>0.80194980184940556</v>
       </c>
     </row>
@@ -4237,11 +9555,11 @@
         <v>746083.11</v>
       </c>
       <c r="E62" s="6">
-        <f>C62/D62*100</f>
+        <f t="shared" si="4"/>
         <v>4.9800993350459306</v>
       </c>
       <c r="F62" s="5">
-        <f>C62/B62</f>
+        <f t="shared" si="5"/>
         <v>3.5899207729468601</v>
       </c>
       <c r="L62" s="7" t="s">
@@ -4257,11 +9575,11 @@
         <v>382753.71</v>
       </c>
       <c r="P62" s="9">
-        <f>N62/O62*100</f>
+        <f t="shared" si="6"/>
         <v>2.2667161083820715</v>
       </c>
       <c r="Q62" s="8">
-        <f>N62/M62</f>
+        <f t="shared" si="7"/>
         <v>0.7920339601971883</v>
       </c>
     </row>
@@ -4279,11 +9597,11 @@
         <v>840077.29</v>
       </c>
       <c r="E63" s="6">
-        <f>C63/D63*100</f>
+        <f t="shared" si="4"/>
         <v>4.3970966052421199</v>
       </c>
       <c r="F63" s="5">
-        <f>C63/B63</f>
+        <f t="shared" si="5"/>
         <v>3.5856154144826249</v>
       </c>
       <c r="L63" s="7" t="s">
@@ -4299,11 +9617,11 @@
         <v>125714.47</v>
       </c>
       <c r="P63" s="9">
-        <f>N63/O63*100</f>
+        <f t="shared" si="6"/>
         <v>2.075051503617682</v>
       </c>
       <c r="Q63" s="8">
-        <f>N63/M63</f>
+        <f t="shared" si="7"/>
         <v>0.64746587242491926</v>
       </c>
     </row>
@@ -4321,11 +9639,11 @@
         <v>994344.98</v>
       </c>
       <c r="E64" s="6">
-        <f>C64/D64*100</f>
+        <f t="shared" si="4"/>
         <v>3.5659947717541653</v>
       </c>
       <c r="F64" s="5">
-        <f>C64/B64</f>
+        <f t="shared" si="5"/>
         <v>1.3598055683387023</v>
       </c>
       <c r="L64" s="7" t="s">
@@ -4341,11 +9659,11 @@
         <v>140947.39000000001</v>
       </c>
       <c r="P64" s="9">
-        <f>N64/O64*100</f>
+        <f t="shared" si="6"/>
         <v>3.9211368156586648</v>
       </c>
       <c r="Q64" s="8">
-        <f>N64/M64</f>
+        <f t="shared" si="7"/>
         <v>0.63141094481891924</v>
       </c>
     </row>
@@ -4363,11 +9681,11 @@
         <v>940960.97</v>
       </c>
       <c r="E65" s="6">
-        <f>C65/D65*100</f>
+        <f t="shared" si="4"/>
         <v>3.74943713127655</v>
       </c>
       <c r="F65" s="5">
-        <f>C65/B65</f>
+        <f t="shared" si="5"/>
         <v>3.5945736118186447</v>
       </c>
       <c r="L65" s="7" t="s">
@@ -4383,11 +9701,11 @@
         <v>212602.13</v>
       </c>
       <c r="P65" s="9">
-        <f>N65/O65*100</f>
+        <f t="shared" si="6"/>
         <v>2.6525039989016101</v>
       </c>
       <c r="Q65" s="8">
-        <f>N65/M65</f>
+        <f t="shared" si="7"/>
         <v>0.53651222528779374</v>
       </c>
     </row>
@@ -4405,11 +9723,11 @@
         <v>790327.5</v>
       </c>
       <c r="E66" s="6">
-        <f>C66/D66*100</f>
+        <f t="shared" ref="E66:E97" si="8">C66/D66*100</f>
         <v>4.416815813697486</v>
       </c>
       <c r="F66" s="5">
-        <f>C66/B66</f>
+        <f t="shared" ref="F66:F100" si="9">C66/B66</f>
         <v>3.7766212268743913</v>
       </c>
       <c r="L66" s="7" t="s">
@@ -4425,11 +9743,11 @@
         <v>150083.92000000001</v>
       </c>
       <c r="P66" s="9">
-        <f>N66/O66*100</f>
+        <f t="shared" ref="P66:P97" si="10">N66/O66*100</f>
         <v>1.7595422614228091</v>
       </c>
       <c r="Q66" s="8">
-        <f>N66/M66</f>
+        <f t="shared" si="7"/>
         <v>0.41804495804970715</v>
       </c>
     </row>
@@ -4447,11 +9765,11 @@
         <v>876011.17</v>
       </c>
       <c r="E67" s="6">
-        <f>C67/D67*100</f>
+        <f t="shared" si="8"/>
         <v>3.9347546219073894</v>
       </c>
       <c r="F67" s="5">
-        <f>C67/B67</f>
+        <f t="shared" si="9"/>
         <v>1.9400512185512466</v>
       </c>
       <c r="L67" s="11" t="s">
@@ -4467,11 +9785,11 @@
         <v>16603.669999999998</v>
       </c>
       <c r="P67" s="13">
-        <f>N67/O67*100</f>
+        <f t="shared" si="10"/>
         <v>1.9513758102877259</v>
       </c>
       <c r="Q67" s="12">
-        <f>N67/M67</f>
+        <f t="shared" si="7"/>
         <v>4.3542534605563767E-2</v>
       </c>
     </row>
@@ -4489,11 +9807,11 @@
         <v>617724.37</v>
       </c>
       <c r="E68" s="6">
-        <f>C68/D68*100</f>
+        <f t="shared" si="8"/>
         <v>5.23422444868089</v>
       </c>
       <c r="F68" s="5">
-        <f>C68/B68</f>
+        <f t="shared" si="9"/>
         <v>2.147093432498838</v>
       </c>
     </row>
@@ -4511,11 +9829,11 @@
         <v>644715.72</v>
       </c>
       <c r="E69" s="6">
-        <f>C69/D69*100</f>
+        <f t="shared" si="8"/>
         <v>4.9196613353867038</v>
       </c>
       <c r="F69" s="5">
-        <f>C69/B69</f>
+        <f t="shared" si="9"/>
         <v>2.9433769487750556</v>
       </c>
     </row>
@@ -4533,11 +9851,11 @@
         <v>981007.93</v>
       </c>
       <c r="E70" s="6">
-        <f>C70/D70*100</f>
+        <f t="shared" si="8"/>
         <v>2.898710512972102</v>
       </c>
       <c r="F70" s="5">
-        <f>C70/B70</f>
+        <f t="shared" si="9"/>
         <v>2.3555815109343938</v>
       </c>
     </row>
@@ -4555,11 +9873,11 @@
         <v>339968.23</v>
       </c>
       <c r="E71" s="6">
-        <f>C71/D71*100</f>
+        <f t="shared" si="8"/>
         <v>8.1735578645098705</v>
       </c>
       <c r="F71" s="5">
-        <f>C71/B71</f>
+        <f t="shared" si="9"/>
         <v>3.6572124243221902</v>
       </c>
     </row>
@@ -4577,11 +9895,11 @@
         <v>651345.05000000005</v>
       </c>
       <c r="E72" s="6">
-        <f>C72/D72*100</f>
+        <f t="shared" si="8"/>
         <v>4.2395685666145768</v>
       </c>
       <c r="F72" s="5">
-        <f>C72/B72</f>
+        <f t="shared" si="9"/>
         <v>1.8498271704180065</v>
       </c>
     </row>
@@ -4599,11 +9917,11 @@
         <v>482178.34</v>
       </c>
       <c r="E73" s="6">
-        <f>C73/D73*100</f>
+        <f t="shared" si="8"/>
         <v>5.6538168014763999</v>
       </c>
       <c r="F73" s="5">
-        <f>C73/B73</f>
+        <f t="shared" si="9"/>
         <v>2.8191809720785934</v>
       </c>
     </row>
@@ -4621,11 +9939,11 @@
         <v>783200.87</v>
       </c>
       <c r="E74" s="6">
-        <f>C74/D74*100</f>
+        <f t="shared" si="8"/>
         <v>3.4653957930358277</v>
       </c>
       <c r="F74" s="5">
-        <f>C74/B74</f>
+        <f t="shared" si="9"/>
         <v>1.4671609276177089</v>
       </c>
     </row>
@@ -4643,11 +9961,11 @@
         <v>848829.42</v>
       </c>
       <c r="E75" s="6">
-        <f>C75/D75*100</f>
+        <f t="shared" si="8"/>
         <v>3.0861442102230621</v>
       </c>
       <c r="F75" s="5">
-        <f>C75/B75</f>
+        <f t="shared" si="9"/>
         <v>1.6707761974615727</v>
       </c>
     </row>
@@ -4665,11 +9983,11 @@
         <v>845731.43</v>
       </c>
       <c r="E76" s="6">
-        <f>C76/D76*100</f>
+        <f t="shared" si="8"/>
         <v>3.0892537599081544</v>
       </c>
       <c r="F76" s="5">
-        <f>C76/B76</f>
+        <f t="shared" si="9"/>
         <v>2.8135677363773421</v>
       </c>
     </row>
@@ -4687,11 +10005,11 @@
         <v>839109.2</v>
       </c>
       <c r="E77" s="6">
-        <f>C77/D77*100</f>
+        <f t="shared" si="8"/>
         <v>3.0593062261741379</v>
       </c>
       <c r="F77" s="5">
-        <f>C77/B77</f>
+        <f t="shared" si="9"/>
         <v>2.3902160148975788</v>
       </c>
     </row>
@@ -4709,11 +10027,11 @@
         <v>603641</v>
       </c>
       <c r="E78" s="6">
-        <f>C78/D78*100</f>
+        <f t="shared" si="8"/>
         <v>4.0114057858892949</v>
       </c>
       <c r="F78" s="5">
-        <f>C78/B78</f>
+        <f t="shared" si="9"/>
         <v>3.4157836084073918</v>
       </c>
     </row>
@@ -4731,11 +10049,11 @@
         <v>548905.25</v>
       </c>
       <c r="E79" s="6">
-        <f>C79/D79*100</f>
+        <f t="shared" si="8"/>
         <v>4.1386614538665834</v>
       </c>
       <c r="F79" s="5">
-        <f>C79/B79</f>
+        <f t="shared" si="9"/>
         <v>2.43330441302485</v>
       </c>
     </row>
@@ -4753,11 +10071,11 @@
         <v>603088.67000000004</v>
       </c>
       <c r="E80" s="6">
-        <f>C80/D80*100</f>
+        <f t="shared" si="8"/>
         <v>3.5675583160930544</v>
       </c>
       <c r="F80" s="5">
-        <f>C80/B80</f>
+        <f t="shared" si="9"/>
         <v>2.8007732361364228</v>
       </c>
     </row>
@@ -4775,11 +10093,11 @@
         <v>399807.53</v>
       </c>
       <c r="E81" s="6">
-        <f>C81/D81*100</f>
+        <f t="shared" si="8"/>
         <v>4.9334138354022494</v>
       </c>
       <c r="F81" s="5">
-        <f>C81/B81</f>
+        <f t="shared" si="9"/>
         <v>1.739190547570761</v>
       </c>
     </row>
@@ -4797,11 +10115,11 @@
         <v>241821.88</v>
       </c>
       <c r="E82" s="6">
-        <f>C82/D82*100</f>
+        <f t="shared" si="8"/>
         <v>7.5372666857109856</v>
       </c>
       <c r="F82" s="5">
-        <f>C82/B82</f>
+        <f t="shared" si="9"/>
         <v>2.9787154763850299</v>
       </c>
     </row>
@@ -4819,11 +10137,11 @@
         <v>548956.25</v>
       </c>
       <c r="E83" s="6">
-        <f>C83/D83*100</f>
+        <f t="shared" si="8"/>
         <v>2.9331317386403746</v>
       </c>
       <c r="F83" s="5">
-        <f>C83/B83</f>
+        <f t="shared" si="9"/>
         <v>1.2944456949915588</v>
       </c>
     </row>
@@ -4841,11 +10159,11 @@
         <v>580658.38</v>
       </c>
       <c r="E84" s="6">
-        <f>C84/D84*100</f>
+        <f t="shared" si="8"/>
         <v>2.6897467664205585</v>
       </c>
       <c r="F84" s="5">
-        <f>C84/B84</f>
+        <f t="shared" si="9"/>
         <v>1.7552528658125421</v>
       </c>
     </row>
@@ -4863,11 +10181,11 @@
         <v>399080.61</v>
       </c>
       <c r="E85" s="6">
-        <f>C85/D85*100</f>
+        <f t="shared" si="8"/>
         <v>3.2301318773668304</v>
       </c>
       <c r="F85" s="5">
-        <f>C85/B85</f>
+        <f t="shared" si="9"/>
         <v>0.86707674715813543</v>
       </c>
     </row>
@@ -4885,11 +10203,11 @@
         <v>405592.83</v>
       </c>
       <c r="E86" s="6">
-        <f>C86/D86*100</f>
+        <f t="shared" si="8"/>
         <v>3.0035023055018009</v>
       </c>
       <c r="F86" s="5">
-        <f>C86/B86</f>
+        <f t="shared" si="9"/>
         <v>0.97823737252067777</v>
       </c>
     </row>
@@ -4907,11 +10225,11 @@
         <v>417543.16</v>
       </c>
       <c r="E87" s="6">
-        <f>C87/D87*100</f>
+        <f t="shared" si="8"/>
         <v>2.7289969257309834</v>
       </c>
       <c r="F87" s="5">
-        <f>C87/B87</f>
+        <f t="shared" si="9"/>
         <v>1.4297038895859473</v>
       </c>
     </row>
@@ -4929,11 +10247,11 @@
         <v>344176.87</v>
       </c>
       <c r="E88" s="6">
-        <f>C88/D88*100</f>
+        <f t="shared" si="8"/>
         <v>3.2134872979697908</v>
       </c>
       <c r="F88" s="5">
-        <f>C88/B88</f>
+        <f t="shared" si="9"/>
         <v>1.7115567935623646</v>
       </c>
     </row>
@@ -4951,11 +10269,11 @@
         <v>500771.13</v>
       </c>
       <c r="E89" s="6">
-        <f>C89/D89*100</f>
+        <f t="shared" si="8"/>
         <v>2.065103074132888</v>
       </c>
       <c r="F89" s="5">
-        <f>C89/B89</f>
+        <f t="shared" si="9"/>
         <v>1.4146976744186046</v>
       </c>
     </row>
@@ -4973,11 +10291,11 @@
         <v>248492.15</v>
       </c>
       <c r="E90" s="6">
-        <f>C90/D90*100</f>
+        <f t="shared" si="8"/>
         <v>3.7835601647778412</v>
       </c>
       <c r="F90" s="5">
-        <f>C90/B90</f>
+        <f t="shared" si="9"/>
         <v>1.1117240156083719</v>
       </c>
     </row>
@@ -4995,11 +10313,11 @@
         <v>351079.49</v>
       </c>
       <c r="E91" s="6">
-        <f>C91/D91*100</f>
+        <f t="shared" si="8"/>
         <v>2.6368843135781015</v>
       </c>
       <c r="F91" s="5">
-        <f>C91/B91</f>
+        <f t="shared" si="9"/>
         <v>0.81299376481953101</v>
       </c>
     </row>
@@ -5017,11 +10335,11 @@
         <v>382753.71</v>
       </c>
       <c r="E92" s="6">
-        <f>C92/D92*100</f>
+        <f t="shared" si="8"/>
         <v>2.2667161083820715</v>
       </c>
       <c r="F92" s="5">
-        <f>C92/B92</f>
+        <f t="shared" si="9"/>
         <v>0.7920339601971883</v>
       </c>
     </row>
@@ -5039,11 +10357,11 @@
         <v>98824.4</v>
       </c>
       <c r="E93" s="6">
-        <f>C93/D93*100</f>
+        <f t="shared" si="8"/>
         <v>7.3144081825945824</v>
       </c>
       <c r="F93" s="5">
-        <f>C93/B93</f>
+        <f t="shared" si="9"/>
         <v>1.1289114477588631</v>
       </c>
     </row>
@@ -5061,11 +10379,11 @@
         <v>260151.48</v>
       </c>
       <c r="E94" s="6">
-        <f>C94/D94*100</f>
+        <f t="shared" si="8"/>
         <v>2.3335481312656765</v>
       </c>
       <c r="F94" s="5">
-        <f>C94/B94</f>
+        <f t="shared" si="9"/>
         <v>0.80194980184940556</v>
       </c>
     </row>
@@ -5083,11 +10401,11 @@
         <v>212602.13</v>
       </c>
       <c r="E95" s="6">
-        <f>C95/D95*100</f>
+        <f t="shared" si="8"/>
         <v>2.6525039989016101</v>
       </c>
       <c r="F95" s="5">
-        <f>C95/B95</f>
+        <f t="shared" si="9"/>
         <v>0.53651222528779374</v>
       </c>
     </row>
@@ -5105,11 +10423,11 @@
         <v>140947.39000000001</v>
       </c>
       <c r="E96" s="6">
-        <f>C96/D96*100</f>
+        <f t="shared" si="8"/>
         <v>3.9211368156586648</v>
       </c>
       <c r="F96" s="5">
-        <f>C96/B96</f>
+        <f t="shared" si="9"/>
         <v>0.63141094481891924</v>
       </c>
     </row>
@@ -5127,11 +10445,11 @@
         <v>198067.73</v>
       </c>
       <c r="E97" s="6">
-        <f>C97/D97*100</f>
+        <f t="shared" si="8"/>
         <v>2.2891209991652857</v>
       </c>
       <c r="F97" s="5">
-        <f>C97/B97</f>
+        <f t="shared" si="9"/>
         <v>0.88365036055349844</v>
       </c>
     </row>
@@ -5149,11 +10467,11 @@
         <v>150083.92000000001</v>
       </c>
       <c r="E98" s="6">
-        <f>C98/D98*100</f>
+        <f t="shared" ref="E98:E129" si="11">C98/D98*100</f>
         <v>1.7595422614228091</v>
       </c>
       <c r="F98" s="5">
-        <f>C98/B98</f>
+        <f t="shared" si="9"/>
         <v>0.41804495804970715</v>
       </c>
     </row>
@@ -5171,11 +10489,11 @@
         <v>125714.47</v>
       </c>
       <c r="E99" s="6">
-        <f>C99/D99*100</f>
+        <f t="shared" si="11"/>
         <v>2.075051503617682</v>
       </c>
       <c r="F99" s="5">
-        <f>C99/B99</f>
+        <f t="shared" si="9"/>
         <v>0.64746587242491926</v>
       </c>
     </row>
@@ -5193,19 +10511,188 @@
         <v>16603.669999999998</v>
       </c>
       <c r="E100" s="6">
-        <f>C100/D100*100</f>
+        <f t="shared" si="11"/>
         <v>1.9513758102877259</v>
       </c>
       <c r="F100" s="5">
-        <f>C100/B100</f>
+        <f t="shared" si="9"/>
         <v>4.3542534605563767E-2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
   <tableParts count="2">
-    <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26BE1DB6-A84C-4EEE-ACE0-FB7510F0E179}">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" s="32">
+        <v>430640</v>
+      </c>
+      <c r="C2" s="23">
+        <v>4998921</v>
+      </c>
+      <c r="D2" s="23">
+        <v>86397461.790000007</v>
+      </c>
+      <c r="E2" s="24">
+        <f t="shared" ref="E2:E7" si="0">C2/D2*100</f>
+        <v>5.7859581710288106</v>
+      </c>
+      <c r="F2" s="25">
+        <f t="shared" ref="F2:F7" si="1">C2/B2</f>
+        <v>11.608120471855843</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="B3" s="33">
+        <v>165224</v>
+      </c>
+      <c r="C3" s="26">
+        <v>1741874.47</v>
+      </c>
+      <c r="D3" s="26">
+        <v>27902848.670000002</v>
+      </c>
+      <c r="E3" s="27">
+        <f t="shared" si="0"/>
+        <v>6.2426402787783886</v>
+      </c>
+      <c r="F3" s="28">
+        <f t="shared" si="1"/>
+        <v>10.542502723575268</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="32">
+        <v>211226</v>
+      </c>
+      <c r="C4" s="23">
+        <v>1692016.44</v>
+      </c>
+      <c r="D4" s="23">
+        <v>34460047.490000002</v>
+      </c>
+      <c r="E4" s="24">
+        <f t="shared" si="0"/>
+        <v>4.9100815676211944</v>
+      </c>
+      <c r="F4" s="25">
+        <f t="shared" si="1"/>
+        <v>8.0104553416719533</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" s="33">
+        <v>130882</v>
+      </c>
+      <c r="C5" s="26">
+        <v>1471673.94</v>
+      </c>
+      <c r="D5" s="26">
+        <v>24200402.25</v>
+      </c>
+      <c r="E5" s="27">
+        <f t="shared" si="0"/>
+        <v>6.0811961916872681</v>
+      </c>
+      <c r="F5" s="28">
+        <f t="shared" si="1"/>
+        <v>11.244280649745573</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" s="32">
+        <v>131090</v>
+      </c>
+      <c r="C6" s="23">
+        <v>1169665.99</v>
+      </c>
+      <c r="D6" s="23">
+        <v>22967283.289999999</v>
+      </c>
+      <c r="E6" s="24">
+        <f t="shared" si="0"/>
+        <v>5.092748564255638</v>
+      </c>
+      <c r="F6" s="25">
+        <f t="shared" si="1"/>
+        <v>8.9226179723853836</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="33">
+        <v>16667</v>
+      </c>
+      <c r="C7" s="26">
+        <v>355642.88</v>
+      </c>
+      <c r="D7" s="26">
+        <v>5142111.9000000004</v>
+      </c>
+      <c r="E7" s="27">
+        <f t="shared" si="0"/>
+        <v>6.9162804488949376</v>
+      </c>
+      <c r="F7" s="28">
+        <f t="shared" si="1"/>
+        <v>21.338146037079259</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>